--- a/Intraday/Output/2026/July/2026-07-24/intraday_accuracy_report.xlsx
+++ b/Intraday/Output/2026/July/2026-07-24/intraday_accuracy_report.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>171</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="7">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.16</v>
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>1668.4</v>
+        <v>1676.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1617.2</v>
+        <v>1621.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>1665.7</v>
+        <v>1673.7</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
@@ -939,32 +939,32 @@
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>1445.7</v>
+        <v>1452</v>
       </c>
       <c r="AG3" t="n">
-        <v>1384.2</v>
+        <v>1403</v>
       </c>
       <c r="AH3" t="n">
-        <v>1428.9</v>
+        <v>1416.7</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>STOP LOSS HIT</t>
+          <t>EOD EXIT</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Stop loss breached during replay range</t>
+          <t>Neither target nor stop reached; exited at close</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>1400.91</v>
+        <v>1416.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>-28.58999999999992</v>
+        <v>-12.79999999999996</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1.999999999999994</v>
+        <v>-0.8954179783140926</v>
       </c>
       <c r="AN3" t="b">
         <v>0</v>
@@ -1071,13 +1071,13 @@
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>4085</v>
+        <v>4052</v>
       </c>
       <c r="AG4" t="n">
-        <v>4013.1</v>
+        <v>3984.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>4079.4</v>
+        <v>4010.4</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
@@ -1090,13 +1090,13 @@
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>4079.4</v>
+        <v>4010.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>-6.700000000000273</v>
+        <v>62.29999999999973</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.1645100302011018</v>
+        <v>1.529697743511669</v>
       </c>
       <c r="AN4" t="b">
         <v>0</v>
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>76051.45</v>
+        <v>76620</v>
       </c>
       <c r="AG5" t="n">
-        <v>75700</v>
+        <v>75940</v>
       </c>
       <c r="AH5" t="n">
-        <v>75800</v>
+        <v>76568.85000000001</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>75800</v>
+        <v>76568.85000000001</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-768.8500000000058</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-1.014313984168873</v>
       </c>
       <c r="AN5" t="b">
         <v>0</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>771.8</v>
+        <v>769.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>745.05</v>
+        <v>744.65</v>
       </c>
       <c r="AH6" t="n">
-        <v>758.4</v>
+        <v>764.45</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
@@ -1354,13 +1354,13 @@
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>758.4</v>
+        <v>764.45</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.8999999999999773</v>
+        <v>-6.950000000000045</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.1188118811881158</v>
+        <v>-0.9174917491749236</v>
       </c>
       <c r="AN6" t="b">
         <v>0</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1584.1</v>
+        <v>1576.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1541</v>
+        <v>1530.1</v>
       </c>
       <c r="AH7" t="n">
         <v>1558.7</v>
@@ -1599,13 +1599,13 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>1808</v>
+        <v>1825</v>
       </c>
       <c r="AG8" t="n">
-        <v>1789.5</v>
+        <v>1763.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1801</v>
+        <v>1809.7</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>1801</v>
+        <v>1809.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.7000000000000455</v>
+        <v>-8</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0388521951490284</v>
+        <v>-0.444025087417439</v>
       </c>
       <c r="AN8" t="b">
         <v>0</v>
@@ -1731,13 +1731,13 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>56420</v>
+        <v>57168</v>
       </c>
       <c r="AG9" t="n">
-        <v>56220</v>
+        <v>56400</v>
       </c>
       <c r="AH9" t="n">
-        <v>56274.6</v>
+        <v>57086.6</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>56274.6</v>
+        <v>57086.6</v>
       </c>
       <c r="AL9" t="n">
-        <v>-24.40000000000145</v>
+        <v>-836.4000000000015</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.0433776235462299</v>
+        <v>-1.48692804647806</v>
       </c>
       <c r="AN9" t="b">
         <v>0</v>
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>5389</v>
+        <v>5395.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>5314.5</v>
+        <v>5258.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>5343.5</v>
+        <v>5315.5</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>5343.5</v>
+        <v>5315.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.5</v>
+        <v>27.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.009358038555118801</v>
+        <v>0.5146921205315366</v>
       </c>
       <c r="AN10" t="b">
         <v>0</v>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1245.4</v>
+        <v>1217</v>
       </c>
       <c r="AG11" t="n">
-        <v>1219.4</v>
+        <v>1183.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1231.2</v>
+        <v>1209.8</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>1231.2</v>
+        <v>1209.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>-3.400000000000091</v>
+        <v>18</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.2769180648314132</v>
+        <v>1.466036813813325</v>
       </c>
       <c r="AN11" t="b">
         <v>0</v>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>588.85</v>
+        <v>589.35</v>
       </c>
       <c r="AG12" t="n">
-        <v>578</v>
+        <v>573.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>580.35</v>
+        <v>576.45</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
@@ -2146,13 +2146,13 @@
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>580.35</v>
+        <v>576.45</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.3500000000000227</v>
+        <v>3.549999999999955</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.0603448275862108</v>
+        <v>0.6120689655172336</v>
       </c>
       <c r="AN12" t="b">
         <v>0</v>
@@ -2259,32 +2259,32 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>2989</v>
+        <v>3018.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>2936.4</v>
+        <v>2941</v>
       </c>
       <c r="AH13" t="n">
-        <v>2943</v>
+        <v>3004.7</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK13" t="n">
-        <v>2943</v>
+        <v>2998.086</v>
       </c>
       <c r="AL13" t="n">
-        <v>-3.699999999999818</v>
+        <v>-58.7859999999996</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.1258803116388193</v>
+        <v>-1.999999999999986</v>
       </c>
       <c r="AN13" t="b">
         <v>0</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>4913</v>
+        <v>4841</v>
       </c>
       <c r="AG14" t="n">
-        <v>4828.5</v>
+        <v>4725</v>
       </c>
       <c r="AH14" t="n">
-        <v>4848</v>
+        <v>4817.5</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
@@ -2410,13 +2410,13 @@
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>4848</v>
+        <v>4817.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.5</v>
+        <v>35</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0927357032457496</v>
+        <v>0.7212776919113859</v>
       </c>
       <c r="AN14" t="b">
         <v>0</v>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>571.7</v>
+        <v>579.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AH15" t="n">
-        <v>569.2</v>
+        <v>575.65</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>569.2</v>
+        <v>575.65</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>-6.449999999999932</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-1.133169360505961</v>
       </c>
       <c r="AN15" t="b">
         <v>0</v>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>604.15</v>
+        <v>608</v>
       </c>
       <c r="AG16" t="n">
-        <v>594</v>
+        <v>598.95</v>
       </c>
       <c r="AH16" t="n">
-        <v>600.7</v>
+        <v>606.25</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>600.7</v>
+        <v>606.25</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.349999999999909</v>
+        <v>-5.200000000000045</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.0582314283337341</v>
+        <v>-0.8651526495299967</v>
       </c>
       <c r="AN16" t="b">
         <v>0</v>
@@ -2787,13 +2787,13 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>351.95</v>
+        <v>354.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>345.4</v>
+        <v>347.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>350.1</v>
+        <v>353.45</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>350.1</v>
+        <v>353.45</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1.050000000000011</v>
+        <v>-4.399999999999977</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.3008165019338236</v>
+        <v>-1.260564389056002</v>
       </c>
       <c r="AN17" t="b">
         <v>0</v>
@@ -2919,13 +2919,13 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>872.95</v>
+        <v>870.45</v>
       </c>
       <c r="AG18" t="n">
-        <v>859.3</v>
+        <v>848.95</v>
       </c>
       <c r="AH18" t="n">
-        <v>862.6</v>
+        <v>852.45</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
@@ -2938,13 +2938,13 @@
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>862.6</v>
+        <v>852.45</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.5</v>
+        <v>12.64999999999998</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.2889839324933533</v>
+        <v>1.462258698416365</v>
       </c>
       <c r="AN18" t="b">
         <v>0</v>
@@ -3051,13 +3051,13 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1321</v>
+        <v>1340.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>1300</v>
+        <v>1305.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1316.5</v>
+        <v>1331.2</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>1316.5</v>
+        <v>1331.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.299999999999954</v>
+        <v>-16</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0.0988442822384393</v>
+        <v>-1.21654501216545</v>
       </c>
       <c r="AN19" t="b">
         <v>0</v>
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>7413</v>
+        <v>7422</v>
       </c>
       <c r="AG20" t="n">
-        <v>7312</v>
+        <v>7189</v>
       </c>
       <c r="AH20" t="n">
-        <v>7333</v>
+        <v>7237.5</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>7333</v>
+        <v>7237.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>-11</v>
+        <v>84.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0.1502321770008194</v>
+        <v>1.154056268779022</v>
       </c>
       <c r="AN20" t="b">
         <v>0</v>
@@ -3315,13 +3315,13 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>13779</v>
+        <v>13740</v>
       </c>
       <c r="AG21" t="n">
-        <v>13641</v>
+        <v>13390</v>
       </c>
       <c r="AH21" t="n">
-        <v>13641</v>
+        <v>13678</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>13641</v>
+        <v>13678</v>
       </c>
       <c r="AL21" t="n">
-        <v>-9</v>
+        <v>-46</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.06602112676056331</v>
+        <v>-0.3374413145539906</v>
       </c>
       <c r="AN21" t="b">
         <v>0</v>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1175.05</v>
+        <v>1179.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1140.5</v>
+        <v>1151.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1163.2</v>
+        <v>1169.6</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
@@ -3466,13 +3466,13 @@
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>1163.2</v>
+        <v>1169.6</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.2000000000000454</v>
+        <v>-6.599999999999909</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.0171969045571836</v>
+        <v>-0.5674978503869226</v>
       </c>
       <c r="AN22" t="b">
         <v>0</v>
@@ -3579,32 +3579,32 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>421.15</v>
+        <v>429.3</v>
       </c>
       <c r="AG23" t="n">
-        <v>417.2</v>
+        <v>417.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>418.7</v>
+        <v>426.5</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>418.7</v>
+        <v>427.278</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.1999999999999886</v>
+        <v>-8.378000000000043</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0477440916686532</v>
+        <v>-2.000000000000011</v>
       </c>
       <c r="AN23" t="b">
         <v>0</v>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>23774.3</v>
+        <v>23906</v>
       </c>
       <c r="AG24" t="n">
-        <v>23685.7</v>
+        <v>23701</v>
       </c>
       <c r="AH24" t="n">
-        <v>23696.9</v>
+        <v>23874.6</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
@@ -3730,13 +3730,13 @@
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>23696.9</v>
+        <v>23874.6</v>
       </c>
       <c r="AL24" t="n">
-        <v>3</v>
+        <v>-174.6999999999971</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.0126582812585707</v>
+        <v>-0.7371339119574222</v>
       </c>
       <c r="AN24" t="b">
         <v>0</v>
@@ -3843,13 +3843,13 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>25920</v>
+        <v>26182.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>25843.2</v>
+        <v>25899.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>25850</v>
+        <v>26082</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="AK25" t="n">
-        <v>25850</v>
+        <v>26082</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>-232</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>-0.897485493230174</v>
       </c>
       <c r="AN25" t="b">
         <v>0</v>
@@ -3975,32 +3975,32 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>558.9</v>
+        <v>575.45</v>
       </c>
       <c r="AG26" t="n">
-        <v>545.05</v>
+        <v>534.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>552.55</v>
+        <v>571.65</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK26" t="n">
-        <v>552.55</v>
+        <v>561.255</v>
       </c>
       <c r="AL26" t="n">
-        <v>-2.299999999999955</v>
+        <v>-11.005</v>
       </c>
       <c r="AM26" t="n">
-        <v>-0.4179918218991285</v>
+        <v>-1.999999999999999</v>
       </c>
       <c r="AN26" t="b">
         <v>0</v>
@@ -4103,13 +4103,13 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>413.25</v>
+        <v>411.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>405.45</v>
+        <v>401.8</v>
       </c>
       <c r="AH27" t="n">
-        <v>410.3</v>
+        <v>409.5</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
@@ -4122,13 +4122,13 @@
         </is>
       </c>
       <c r="AK27" t="n">
-        <v>410.3</v>
+        <v>409.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.4499999999999886</v>
+        <v>0.3500000000000227</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0.1097962669269217</v>
+        <v>0.0853970964987245</v>
       </c>
       <c r="AN27" t="b">
         <v>0</v>
@@ -4235,13 +4235,13 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>13350</v>
+        <v>13444</v>
       </c>
       <c r="AG28" t="n">
-        <v>13114</v>
+        <v>13059</v>
       </c>
       <c r="AH28" t="n">
-        <v>13226</v>
+        <v>13377</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
@@ -4254,13 +4254,13 @@
         </is>
       </c>
       <c r="AK28" t="n">
-        <v>13226</v>
+        <v>13377</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>-151</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>-1.141690609405716</v>
       </c>
       <c r="AN28" t="b">
         <v>0</v>
@@ -4367,13 +4367,13 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>2719.8</v>
+        <v>2702.1</v>
       </c>
       <c r="AG29" t="n">
-        <v>2683.5</v>
+        <v>2648.7</v>
       </c>
       <c r="AH29" t="n">
-        <v>2690.4</v>
+        <v>2684.6</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
@@ -4386,13 +4386,13 @@
         </is>
       </c>
       <c r="AK29" t="n">
-        <v>2690.4</v>
+        <v>2684.6</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.099999999999909</v>
+        <v>5.900000000000091</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.003716781267419</v>
+        <v>0.2192900947779257</v>
       </c>
       <c r="AN29" t="b">
         <v>0</v>
@@ -4499,32 +4499,32 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>233.48</v>
+        <v>236.45</v>
       </c>
       <c r="AG30" t="n">
-        <v>231.01</v>
+        <v>231.11</v>
       </c>
       <c r="AH30" t="n">
-        <v>232.12</v>
+        <v>235.54</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>232.12</v>
+        <v>236.4054</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.3499999999999943</v>
+        <v>-4.635399999999976</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.1510117789187532</v>
+        <v>-1.999999999999989</v>
       </c>
       <c r="AN30" t="b">
         <v>0</v>
@@ -4631,13 +4631,13 @@
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>405.65</v>
+        <v>408.6</v>
       </c>
       <c r="AG31" t="n">
-        <v>401.35</v>
+        <v>403.15</v>
       </c>
       <c r="AH31" t="n">
-        <v>404.55</v>
+        <v>407.35</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
@@ -4650,13 +4650,13 @@
         </is>
       </c>
       <c r="AK31" t="n">
-        <v>404.55</v>
+        <v>407.35</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.6999999999999886</v>
+        <v>-3.5</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0.1733316825554014</v>
+        <v>-0.866658412777021</v>
       </c>
       <c r="AN31" t="b">
         <v>0</v>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>22.9</v>
+        <v>23.14</v>
       </c>
       <c r="AG32" t="n">
-        <v>22.52</v>
+        <v>22.77</v>
       </c>
       <c r="AH32" t="n">
-        <v>22.79</v>
+        <v>23.09</v>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="AK32" t="n">
-        <v>22.79</v>
+        <v>23.09</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.0199999999999995</v>
+        <v>-0.3200000000000003</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.08783487044356419</v>
+        <v>-1.405357927097059</v>
       </c>
       <c r="AN32" t="b">
         <v>0</v>
@@ -4891,32 +4891,32 @@
         </is>
       </c>
       <c r="AF33" t="n">
-        <v>527.25</v>
+        <v>536.55</v>
       </c>
       <c r="AG33" t="n">
-        <v>525.1</v>
+        <v>525.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>526</v>
+        <v>534.7</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK33" t="n">
-        <v>526</v>
+        <v>536.2140000000001</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.2999999999999545</v>
+        <v>-10.51400000000001</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.0570667681186902</v>
+        <v>-2.000000000000002</v>
       </c>
       <c r="AN33" t="b">
         <v>0</v>
@@ -5023,13 +5023,13 @@
         </is>
       </c>
       <c r="AF34" t="n">
-        <v>1631.8</v>
+        <v>1646.7</v>
       </c>
       <c r="AG34" t="n">
-        <v>1605.7</v>
+        <v>1601.6</v>
       </c>
       <c r="AH34" t="n">
-        <v>1616.5</v>
+        <v>1632.5</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
@@ -5042,13 +5042,13 @@
         </is>
       </c>
       <c r="AK34" t="n">
-        <v>1616.5</v>
+        <v>1632.5</v>
       </c>
       <c r="AL34" t="n">
-        <v>-2</v>
+        <v>-18</v>
       </c>
       <c r="AM34" t="n">
-        <v>-0.1238773614122019</v>
+        <v>-1.114896252709817</v>
       </c>
       <c r="AN34" t="b">
         <v>0</v>
@@ -5155,32 +5155,32 @@
         </is>
       </c>
       <c r="AF35" t="n">
-        <v>1522.6</v>
+        <v>1557.2</v>
       </c>
       <c r="AG35" t="n">
-        <v>1510</v>
+        <v>1512.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>1511.8</v>
+        <v>1546.4</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK35" t="n">
-        <v>1511.8</v>
+        <v>1542.546</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.5</v>
+        <v>-30.24600000000009</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.0330622231038815</v>
+        <v>-2.000000000000006</v>
       </c>
       <c r="AN35" t="b">
         <v>0</v>
@@ -5287,32 +5287,32 @@
         </is>
       </c>
       <c r="AF36" t="n">
-        <v>2044.8</v>
+        <v>2110</v>
       </c>
       <c r="AG36" t="n">
-        <v>2023</v>
+        <v>1990.4</v>
       </c>
       <c r="AH36" t="n">
-        <v>2039.8</v>
+        <v>2100.7</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK36" t="n">
-        <v>2039.8</v>
+        <v>2080.596</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>-40.79600000000005</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AN36" t="b">
         <v>0</v>
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="AF37" t="n">
-        <v>2389</v>
+        <v>2399.8</v>
       </c>
       <c r="AG37" t="n">
-        <v>2363.6</v>
+        <v>2350.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>2385.2</v>
+        <v>2384.8</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
@@ -5438,13 +5438,13 @@
         </is>
       </c>
       <c r="AK37" t="n">
-        <v>2385.2</v>
+        <v>2384.8</v>
       </c>
       <c r="AL37" t="n">
-        <v>-1.699999999999818</v>
+        <v>-1.300000000000182</v>
       </c>
       <c r="AM37" t="n">
-        <v>-0.0713236836584778</v>
+        <v>-0.0545416404447317</v>
       </c>
       <c r="AN37" t="b">
         <v>0</v>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="AF38" t="n">
-        <v>11820</v>
+        <v>11919</v>
       </c>
       <c r="AG38" t="n">
-        <v>11700</v>
+        <v>11682</v>
       </c>
       <c r="AH38" t="n">
-        <v>11747</v>
+        <v>11892</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="AK38" t="n">
-        <v>11747</v>
+        <v>11892</v>
       </c>
       <c r="AL38" t="n">
-        <v>-3</v>
+        <v>-148</v>
       </c>
       <c r="AM38" t="n">
-        <v>-0.0255449591280653</v>
+        <v>-1.260217983651226</v>
       </c>
       <c r="AN38" t="b">
         <v>0</v>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="AF39" t="n">
-        <v>226.36</v>
+        <v>223.72</v>
       </c>
       <c r="AG39" t="n">
-        <v>220.44</v>
+        <v>218.03</v>
       </c>
       <c r="AH39" t="n">
-        <v>223.67</v>
+        <v>222.05</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
@@ -5702,13 +5702,13 @@
         </is>
       </c>
       <c r="AK39" t="n">
-        <v>223.67</v>
+        <v>222.05</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.1599999999999966</v>
+        <v>1.45999999999998</v>
       </c>
       <c r="AM39" t="n">
-        <v>-0.07158516397476471</v>
+        <v>0.6532146212697327</v>
       </c>
       <c r="AN39" t="b">
         <v>0</v>
@@ -5815,14 +5815,14 @@
         </is>
       </c>
       <c r="AF40" t="n">
+        <v>469</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>460.95</v>
+      </c>
+      <c r="AH40" t="n">
         <v>464.5</v>
       </c>
-      <c r="AG40" t="n">
-        <v>458.85</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>462.2</v>
-      </c>
       <c r="AI40" t="inlineStr">
         <is>
           <t>EOD EXIT</t>
@@ -5834,13 +5834,13 @@
         </is>
       </c>
       <c r="AK40" t="n">
-        <v>462.2</v>
+        <v>464.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.800000000000011</v>
+        <v>-0.5</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.387931034482761</v>
+        <v>-0.1077586206896551</v>
       </c>
       <c r="AN40" t="b">
         <v>0</v>
@@ -5947,32 +5947,32 @@
         </is>
       </c>
       <c r="AF41" t="n">
-        <v>391.65</v>
+        <v>397.15</v>
       </c>
       <c r="AG41" t="n">
-        <v>384.35</v>
+        <v>386</v>
       </c>
       <c r="AH41" t="n">
-        <v>385.5</v>
+        <v>395.65</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK41" t="n">
-        <v>385.5</v>
+        <v>393.567</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.3500000000000227</v>
+        <v>-7.716999999999984</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.09070882467280619</v>
+        <v>-1.999999999999996</v>
       </c>
       <c r="AN41" t="b">
         <v>0</v>
@@ -6079,13 +6079,13 @@
         </is>
       </c>
       <c r="AF42" t="n">
-        <v>352.55</v>
+        <v>356.75</v>
       </c>
       <c r="AG42" t="n">
-        <v>349</v>
+        <v>349.95</v>
       </c>
       <c r="AH42" t="n">
-        <v>351.95</v>
+        <v>355</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>351.95</v>
+        <v>355</v>
       </c>
       <c r="AL42" t="n">
-        <v>-0.8999999999999773</v>
+        <v>-3.949999999999989</v>
       </c>
       <c r="AM42" t="n">
-        <v>-0.2563737359350455</v>
+        <v>-1.12519584104828</v>
       </c>
       <c r="AN42" t="b">
         <v>0</v>
@@ -6211,32 +6211,32 @@
         </is>
       </c>
       <c r="AF43" t="n">
-        <v>248.5</v>
+        <v>253.2</v>
       </c>
       <c r="AG43" t="n">
-        <v>243.9</v>
+        <v>241.75</v>
       </c>
       <c r="AH43" t="n">
-        <v>244.1</v>
+        <v>251.95</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK43" t="n">
-        <v>244.1</v>
+        <v>248.676</v>
       </c>
       <c r="AL43" t="n">
-        <v>-0.2999999999999829</v>
+        <v>-4.875999999999976</v>
       </c>
       <c r="AM43" t="n">
-        <v>-0.1230516817063096</v>
+        <v>-1.99999999999999</v>
       </c>
       <c r="AN43" t="b">
         <v>0</v>
@@ -6343,13 +6343,13 @@
         </is>
       </c>
       <c r="AF44" t="n">
-        <v>1158.4</v>
+        <v>1160.8</v>
       </c>
       <c r="AG44" t="n">
-        <v>1135.3</v>
+        <v>1134</v>
       </c>
       <c r="AH44" t="n">
-        <v>1147.9</v>
+        <v>1150.4</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
@@ -6362,13 +6362,13 @@
         </is>
       </c>
       <c r="AK44" t="n">
-        <v>1147.9</v>
+        <v>1150.4</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.5</v>
+        <v>-3</v>
       </c>
       <c r="AM44" t="n">
-        <v>-0.0435767822903956</v>
+        <v>-0.261460693742374</v>
       </c>
       <c r="AN44" t="b">
         <v>0</v>
@@ -6475,32 +6475,32 @@
         </is>
       </c>
       <c r="AF45" t="n">
-        <v>93</v>
+        <v>94.56</v>
       </c>
       <c r="AG45" t="n">
-        <v>90</v>
+        <v>91.78</v>
       </c>
       <c r="AH45" t="n">
-        <v>92.06999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>92.06999999999999</v>
+        <v>93.9114</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>-1.841400000000008</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>-2.000000000000008</v>
       </c>
       <c r="AN45" t="b">
         <v>0</v>
@@ -6607,13 +6607,13 @@
         </is>
       </c>
       <c r="AF46" t="n">
-        <v>2302.3</v>
+        <v>2296.8</v>
       </c>
       <c r="AG46" t="n">
-        <v>2280.7</v>
+        <v>2247</v>
       </c>
       <c r="AH46" t="n">
-        <v>2292.6</v>
+        <v>2274.4</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
@@ -6626,13 +6626,13 @@
         </is>
       </c>
       <c r="AK46" t="n">
-        <v>2292.6</v>
+        <v>2274.4</v>
       </c>
       <c r="AL46" t="n">
-        <v>-2.599999999999909</v>
+        <v>15.59999999999991</v>
       </c>
       <c r="AM46" t="n">
-        <v>-0.1135371179039261</v>
+        <v>0.6812227074235768</v>
       </c>
       <c r="AN46" t="b">
         <v>0</v>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="AF47" t="n">
-        <v>1851.1</v>
+        <v>1869.7</v>
       </c>
       <c r="AG47" t="n">
-        <v>1817.1</v>
+        <v>1773.7</v>
       </c>
       <c r="AH47" t="n">
-        <v>1848.4</v>
+        <v>1803.4</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
@@ -6758,13 +6758,13 @@
         </is>
       </c>
       <c r="AK47" t="n">
-        <v>1848.4</v>
+        <v>1803.4</v>
       </c>
       <c r="AL47" t="n">
-        <v>-3.800000000000182</v>
+        <v>41.19999999999982</v>
       </c>
       <c r="AM47" t="n">
-        <v>-0.206006722324633</v>
+        <v>2.233546568361694</v>
       </c>
       <c r="AN47" t="b">
         <v>0</v>
@@ -6871,13 +6871,13 @@
         </is>
       </c>
       <c r="AF48" t="n">
-        <v>432</v>
+        <v>437.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>426.85</v>
+        <v>429</v>
       </c>
       <c r="AH48" t="n">
-        <v>430.5</v>
+        <v>436.5</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -6890,13 +6890,13 @@
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>430.5</v>
+        <v>436.5</v>
       </c>
       <c r="AL48" t="n">
-        <v>-0.1000000000000227</v>
+        <v>-6.100000000000023</v>
       </c>
       <c r="AM48" t="n">
-        <v>-0.0232342007434997</v>
+        <v>-1.417286245353165</v>
       </c>
       <c r="AN48" t="b">
         <v>0</v>
@@ -7003,35 +7003,35 @@
         </is>
       </c>
       <c r="AF49" t="n">
-        <v>944.3</v>
+        <v>948.05</v>
       </c>
       <c r="AG49" t="n">
-        <v>891.05</v>
+        <v>841</v>
       </c>
       <c r="AH49" t="n">
-        <v>891.6</v>
+        <v>875.75</v>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>STOP LOSS HIT</t>
+          <t>TARGET HIT</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>Stop loss breached during replay range</t>
+          <t>Target reached during replay range</t>
         </is>
       </c>
       <c r="AK49" t="n">
-        <v>908.667</v>
+        <v>855.216</v>
       </c>
       <c r="AL49" t="n">
-        <v>-17.81700000000001</v>
+        <v>35.63400000000001</v>
       </c>
       <c r="AM49" t="n">
-        <v>-2.000000000000001</v>
+        <v>4.000000000000002</v>
       </c>
       <c r="AN49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -7135,32 +7135,32 @@
         </is>
       </c>
       <c r="AF50" t="n">
-        <v>76.2</v>
+        <v>77.75</v>
       </c>
       <c r="AG50" t="n">
-        <v>75.5</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AH50" t="n">
-        <v>75.55</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK50" t="n">
-        <v>75.55</v>
+        <v>76.81620000000001</v>
       </c>
       <c r="AL50" t="n">
-        <v>-0.2399999999999948</v>
+        <v>-1.506200000000007</v>
       </c>
       <c r="AM50" t="n">
-        <v>-0.3186827778515401</v>
+        <v>-2.000000000000009</v>
       </c>
       <c r="AN50" t="b">
         <v>0</v>
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="AF51" t="n">
-        <v>422.75</v>
+        <v>419.7</v>
       </c>
       <c r="AG51" t="n">
-        <v>419.65</v>
+        <v>412.8</v>
       </c>
       <c r="AH51" t="n">
-        <v>421.6</v>
+        <v>416.45</v>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
@@ -7286,13 +7286,13 @@
         </is>
       </c>
       <c r="AK51" t="n">
-        <v>421.6</v>
+        <v>416.45</v>
       </c>
       <c r="AL51" t="n">
-        <v>-0.6000000000000227</v>
+        <v>4.550000000000011</v>
       </c>
       <c r="AM51" t="n">
-        <v>-0.1425178147268462</v>
+        <v>1.080760095011879</v>
       </c>
       <c r="AN51" t="b">
         <v>0</v>
@@ -7399,13 +7399,13 @@
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>174.2</v>
+        <v>172.88</v>
       </c>
       <c r="AG52" t="n">
-        <v>172.2</v>
+        <v>169.08</v>
       </c>
       <c r="AH52" t="n">
-        <v>172.54</v>
+        <v>172.29</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="AK52" t="n">
-        <v>172.54</v>
+        <v>172.29</v>
       </c>
       <c r="AL52" t="n">
-        <v>-0.2299999999999897</v>
+        <v>0.0200000000000102</v>
       </c>
       <c r="AM52" t="n">
-        <v>-0.1334803551738086</v>
+        <v>0.0116069874064246</v>
       </c>
       <c r="AN52" t="b">
         <v>0</v>
@@ -7531,13 +7531,13 @@
         </is>
       </c>
       <c r="AF53" t="n">
-        <v>306.4</v>
+        <v>311.3</v>
       </c>
       <c r="AG53" t="n">
-        <v>298.5</v>
+        <v>302.4</v>
       </c>
       <c r="AH53" t="n">
-        <v>305.7</v>
+        <v>307.95</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
@@ -7550,13 +7550,13 @@
         </is>
       </c>
       <c r="AK53" t="n">
-        <v>305.7</v>
+        <v>307.95</v>
       </c>
       <c r="AL53" t="n">
-        <v>-0.5</v>
+        <v>-2.75</v>
       </c>
       <c r="AM53" t="n">
-        <v>-0.163826998689384</v>
+        <v>-0.901048492791612</v>
       </c>
       <c r="AN53" t="b">
         <v>0</v>
@@ -7663,32 +7663,32 @@
         </is>
       </c>
       <c r="AF54" t="n">
-        <v>1085.5</v>
+        <v>1109.2</v>
       </c>
       <c r="AG54" t="n">
-        <v>1063.1</v>
+        <v>1069.9</v>
       </c>
       <c r="AH54" t="n">
-        <v>1077.6</v>
+        <v>1106</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK54" t="n">
-        <v>1077.6</v>
+        <v>1096.704</v>
       </c>
       <c r="AL54" t="n">
-        <v>-2.399999999999864</v>
+        <v>-21.50400000000013</v>
       </c>
       <c r="AM54" t="n">
-        <v>-0.223214285714273</v>
+        <v>-2.000000000000012</v>
       </c>
       <c r="AN54" t="b">
         <v>0</v>
@@ -7795,13 +7795,13 @@
         </is>
       </c>
       <c r="AF55" t="n">
-        <v>259.5</v>
+        <v>256.8</v>
       </c>
       <c r="AG55" t="n">
-        <v>241.5</v>
+        <v>241</v>
       </c>
       <c r="AH55" t="n">
-        <v>241.99</v>
+        <v>248.48</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
@@ -7927,13 +7927,13 @@
         </is>
       </c>
       <c r="AF56" t="n">
-        <v>1045.9</v>
+        <v>1043.1</v>
       </c>
       <c r="AG56" t="n">
-        <v>1025.2</v>
+        <v>1011.1</v>
       </c>
       <c r="AH56" t="n">
-        <v>1037.3</v>
+        <v>1040.5</v>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="AK56" t="n">
-        <v>1037.3</v>
+        <v>1040.5</v>
       </c>
       <c r="AL56" t="n">
-        <v>-4.099999999999909</v>
+        <v>-7.299999999999954</v>
       </c>
       <c r="AM56" t="n">
-        <v>-0.396825396825388</v>
+        <v>-0.706542779713507</v>
       </c>
       <c r="AN56" t="b">
         <v>0</v>
@@ -8059,32 +8059,32 @@
         </is>
       </c>
       <c r="AF57" t="n">
-        <v>3242.7</v>
+        <v>3161.2</v>
       </c>
       <c r="AG57" t="n">
-        <v>3130.1</v>
+        <v>3050.1</v>
       </c>
       <c r="AH57" t="n">
-        <v>3138.9</v>
+        <v>3109.8</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>STOP LOSS HIT</t>
+          <t>EOD EXIT</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>Stop loss breached during replay range</t>
+          <t>Neither target nor stop reached; exited at close</t>
         </is>
       </c>
       <c r="AK57" t="n">
-        <v>3199.74</v>
+        <v>3109.8</v>
       </c>
       <c r="AL57" t="n">
-        <v>-62.73999999999978</v>
+        <v>27.19999999999981</v>
       </c>
       <c r="AM57" t="n">
-        <v>-1.999999999999993</v>
+        <v>0.8670704494740139</v>
       </c>
       <c r="AN57" t="b">
         <v>0</v>
@@ -8191,32 +8191,32 @@
         </is>
       </c>
       <c r="AF58" t="n">
-        <v>3776.7</v>
+        <v>3827.5</v>
       </c>
       <c r="AG58" t="n">
-        <v>3745.9</v>
+        <v>3743</v>
       </c>
       <c r="AH58" t="n">
-        <v>3746.2</v>
+        <v>3812.5</v>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK58" t="n">
-        <v>3746.2</v>
+        <v>3820.002</v>
       </c>
       <c r="AL58" t="n">
-        <v>-1.099999999999909</v>
+        <v>-74.90200000000004</v>
       </c>
       <c r="AM58" t="n">
-        <v>-0.0293717123708287</v>
+        <v>-2.000000000000001</v>
       </c>
       <c r="AN58" t="b">
         <v>0</v>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="AF59" t="n">
-        <v>5010</v>
+        <v>5055.5</v>
       </c>
       <c r="AG59" t="n">
-        <v>4891</v>
+        <v>4914</v>
       </c>
       <c r="AH59" t="n">
-        <v>4904</v>
+        <v>5020</v>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
@@ -8455,13 +8455,13 @@
         </is>
       </c>
       <c r="AF60" t="n">
-        <v>2756</v>
+        <v>2763.4</v>
       </c>
       <c r="AG60" t="n">
-        <v>2731</v>
+        <v>2700</v>
       </c>
       <c r="AH60" t="n">
-        <v>2746.9</v>
+        <v>2735.2</v>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
@@ -8474,13 +8474,13 @@
         </is>
       </c>
       <c r="AK60" t="n">
-        <v>2746.9</v>
+        <v>2735.2</v>
       </c>
       <c r="AL60" t="n">
-        <v>-0.9000000000000909</v>
+        <v>10.80000000000018</v>
       </c>
       <c r="AM60" t="n">
-        <v>-0.0327749453750943</v>
+        <v>0.3932993445010991</v>
       </c>
       <c r="AN60" t="b">
         <v>0</v>
@@ -8587,13 +8587,13 @@
         </is>
       </c>
       <c r="AF61" t="n">
-        <v>8996.5</v>
+        <v>9029</v>
       </c>
       <c r="AG61" t="n">
-        <v>8880</v>
+        <v>8862</v>
       </c>
       <c r="AH61" t="n">
-        <v>8923</v>
+        <v>8967.5</v>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
@@ -8606,13 +8606,13 @@
         </is>
       </c>
       <c r="AK61" t="n">
-        <v>8923</v>
+        <v>8967.5</v>
       </c>
       <c r="AL61" t="n">
-        <v>4.5</v>
+        <v>-40</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.0504060487258471</v>
+        <v>-0.4480537664519742</v>
       </c>
       <c r="AN61" t="b">
         <v>0</v>
@@ -8719,32 +8719,32 @@
         </is>
       </c>
       <c r="AF62" t="n">
-        <v>1020</v>
+        <v>1057.1</v>
       </c>
       <c r="AG62" t="n">
-        <v>996.7</v>
+        <v>998.1</v>
       </c>
       <c r="AH62" t="n">
-        <v>1005.2</v>
+        <v>1011.9</v>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK62" t="n">
-        <v>1005.2</v>
+        <v>1023.366</v>
       </c>
       <c r="AL62" t="n">
-        <v>-1.900000000000091</v>
+        <v>-20.06600000000003</v>
       </c>
       <c r="AM62" t="n">
-        <v>-0.1893750622944374</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AN62" t="b">
         <v>0</v>
@@ -8851,13 +8851,13 @@
         </is>
       </c>
       <c r="AF63" t="n">
-        <v>2588.6</v>
+        <v>2557.8</v>
       </c>
       <c r="AG63" t="n">
-        <v>2520.2</v>
+        <v>2517.4</v>
       </c>
       <c r="AH63" t="n">
-        <v>2547.8</v>
+        <v>2524.9</v>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="AK63" t="n">
-        <v>2547.8</v>
+        <v>2524.9</v>
       </c>
       <c r="AL63" t="n">
-        <v>2.099999999999909</v>
+        <v>25</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.08235617083022501</v>
+        <v>0.9804306051217694</v>
       </c>
       <c r="AN63" t="b">
         <v>0</v>
@@ -8983,14 +8983,14 @@
         </is>
       </c>
       <c r="AF64" t="n">
+        <v>3599.9</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>3542</v>
+      </c>
+      <c r="AH64" t="n">
         <v>3571</v>
       </c>
-      <c r="AG64" t="n">
-        <v>3530.7</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>3539.2</v>
-      </c>
       <c r="AI64" t="inlineStr">
         <is>
           <t>EOD EXIT</t>
@@ -9002,13 +9002,13 @@
         </is>
       </c>
       <c r="AK64" t="n">
-        <v>3539.2</v>
+        <v>3571</v>
       </c>
       <c r="AL64" t="n">
-        <v>0.7000000000002728</v>
+        <v>-31.09999999999991</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.0197745699031123</v>
+        <v>-0.8785558914093593</v>
       </c>
       <c r="AN64" t="b">
         <v>0</v>
@@ -9115,13 +9115,13 @@
         </is>
       </c>
       <c r="AF65" t="n">
-        <v>1620</v>
+        <v>1630.2</v>
       </c>
       <c r="AG65" t="n">
-        <v>1595.5</v>
+        <v>1590</v>
       </c>
       <c r="AH65" t="n">
-        <v>1599</v>
+        <v>1604.7</v>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
@@ -9134,13 +9134,13 @@
         </is>
       </c>
       <c r="AK65" t="n">
-        <v>1599</v>
+        <v>1604.7</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>-5.700000000000045</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>-0.3564727954971886</v>
       </c>
       <c r="AN65" t="b">
         <v>0</v>
@@ -9247,32 +9247,32 @@
         </is>
       </c>
       <c r="AF66" t="n">
-        <v>166.03</v>
+        <v>167.18</v>
       </c>
       <c r="AG66" t="n">
-        <v>164</v>
+        <v>161.29</v>
       </c>
       <c r="AH66" t="n">
-        <v>164.27</v>
+        <v>165.46</v>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK66" t="n">
-        <v>164.27</v>
+        <v>167.0658</v>
       </c>
       <c r="AL66" t="n">
-        <v>-0.4800000000000182</v>
+        <v>-3.275800000000004</v>
       </c>
       <c r="AM66" t="n">
-        <v>-0.2930581842603444</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AN66" t="b">
         <v>0</v>
@@ -9379,32 +9379,32 @@
         </is>
       </c>
       <c r="AF67" t="n">
-        <v>322</v>
+        <v>327.95</v>
       </c>
       <c r="AG67" t="n">
-        <v>319.6</v>
+        <v>320.05</v>
       </c>
       <c r="AH67" t="n">
-        <v>319.8</v>
+        <v>326.1</v>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK67" t="n">
-        <v>319.8</v>
+        <v>326.145</v>
       </c>
       <c r="AL67" t="n">
-        <v>-0.0500000000000113</v>
+        <v>-6.394999999999982</v>
       </c>
       <c r="AM67" t="n">
-        <v>-0.0156372165754531</v>
+        <v>-1.999999999999994</v>
       </c>
       <c r="AN67" t="b">
         <v>0</v>
@@ -9507,32 +9507,32 @@
         </is>
       </c>
       <c r="AF68" t="n">
-        <v>13.17</v>
+        <v>13.29</v>
       </c>
       <c r="AG68" t="n">
-        <v>12.94</v>
+        <v>12.83</v>
       </c>
       <c r="AH68" t="n">
-        <v>13.01</v>
+        <v>13.23</v>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK68" t="n">
-        <v>13.01</v>
+        <v>13.2498</v>
       </c>
       <c r="AL68" t="n">
-        <v>-0.0199999999999995</v>
+        <v>-0.2598000000000002</v>
       </c>
       <c r="AM68" t="n">
-        <v>-0.1539645881447234</v>
+        <v>-2.000000000000002</v>
       </c>
       <c r="AN68" t="b">
         <v>0</v>
@@ -9639,13 +9639,13 @@
         </is>
       </c>
       <c r="AF69" t="n">
-        <v>2059.5</v>
+        <v>2051</v>
       </c>
       <c r="AG69" t="n">
-        <v>1985.2</v>
+        <v>1990.8</v>
       </c>
       <c r="AH69" t="n">
-        <v>1990.6</v>
+        <v>2024.6</v>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
@@ -9771,13 +9771,13 @@
         </is>
       </c>
       <c r="AF70" t="n">
-        <v>7531</v>
+        <v>7555</v>
       </c>
       <c r="AG70" t="n">
-        <v>7455</v>
+        <v>7309.5</v>
       </c>
       <c r="AH70" t="n">
-        <v>7477.5</v>
+        <v>7360.5</v>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
@@ -9790,13 +9790,13 @@
         </is>
       </c>
       <c r="AK70" t="n">
-        <v>7477.5</v>
+        <v>7360.5</v>
       </c>
       <c r="AL70" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="AM70" t="n">
-        <v>0</v>
+        <v>1.56469408224674</v>
       </c>
       <c r="AN70" t="b">
         <v>0</v>
@@ -9903,13 +9903,13 @@
         </is>
       </c>
       <c r="AF71" t="n">
-        <v>14370.8</v>
+        <v>14515.3</v>
       </c>
       <c r="AG71" t="n">
-        <v>14291.8</v>
+        <v>14272</v>
       </c>
       <c r="AH71" t="n">
-        <v>14310</v>
+        <v>14494.15</v>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
@@ -9922,13 +9922,13 @@
         </is>
       </c>
       <c r="AK71" t="n">
-        <v>14310</v>
+        <v>14494.15</v>
       </c>
       <c r="AL71" t="n">
-        <v>-4.450000000000728</v>
+        <v>-188.6000000000004</v>
       </c>
       <c r="AM71" t="n">
-        <v>-0.0311068081968238</v>
+        <v>-1.318369444026971</v>
       </c>
       <c r="AN71" t="b">
         <v>0</v>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="AF72" t="n">
-        <v>455.7</v>
+        <v>460.75</v>
       </c>
       <c r="AG72" t="n">
-        <v>451.25</v>
+        <v>452.4</v>
       </c>
       <c r="AH72" t="n">
-        <v>453.5</v>
+        <v>459.05</v>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
@@ -10054,13 +10054,13 @@
         </is>
       </c>
       <c r="AK72" t="n">
-        <v>453.5</v>
+        <v>459.05</v>
       </c>
       <c r="AL72" t="n">
-        <v>-0.25</v>
+        <v>-5.800000000000011</v>
       </c>
       <c r="AM72" t="n">
-        <v>-0.0551571980143408</v>
+        <v>-1.279646993932711</v>
       </c>
       <c r="AN72" t="b">
         <v>0</v>
@@ -10167,13 +10167,13 @@
         </is>
       </c>
       <c r="AF73" t="n">
-        <v>479.4</v>
+        <v>485.45</v>
       </c>
       <c r="AG73" t="n">
-        <v>475.55</v>
+        <v>474.85</v>
       </c>
       <c r="AH73" t="n">
-        <v>476.85</v>
+        <v>478.35</v>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
@@ -10186,13 +10186,13 @@
         </is>
       </c>
       <c r="AK73" t="n">
-        <v>476.85</v>
+        <v>478.35</v>
       </c>
       <c r="AL73" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.1047449460563527</v>
+        <v>-0.2094898921127055</v>
       </c>
       <c r="AN73" t="b">
         <v>0</v>
@@ -10299,32 +10299,32 @@
         </is>
       </c>
       <c r="AF74" t="n">
-        <v>242.3</v>
+        <v>248.4</v>
       </c>
       <c r="AG74" t="n">
-        <v>240.6</v>
+        <v>240.4</v>
       </c>
       <c r="AH74" t="n">
-        <v>241.35</v>
+        <v>247.7</v>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK74" t="n">
-        <v>241.35</v>
+        <v>246.279</v>
       </c>
       <c r="AL74" t="n">
-        <v>0.0999999999999943</v>
+        <v>-4.829000000000008</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.0414164423276017</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AN74" t="b">
         <v>0</v>
@@ -10431,32 +10431,32 @@
         </is>
       </c>
       <c r="AF75" t="n">
-        <v>144.75</v>
+        <v>147.65</v>
       </c>
       <c r="AG75" t="n">
-        <v>143.5</v>
+        <v>143.54</v>
       </c>
       <c r="AH75" t="n">
-        <v>143.76</v>
+        <v>146.29</v>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK75" t="n">
-        <v>143.76</v>
+        <v>146.4924</v>
       </c>
       <c r="AL75" t="n">
-        <v>-0.1399999999999863</v>
+        <v>-2.872399999999999</v>
       </c>
       <c r="AM75" t="n">
-        <v>-0.09747945968527109</v>
+        <v>-2</v>
       </c>
       <c r="AN75" t="b">
         <v>0</v>
@@ -10563,13 +10563,13 @@
         </is>
       </c>
       <c r="AF76" t="n">
-        <v>27000</v>
+        <v>26775</v>
       </c>
       <c r="AG76" t="n">
-        <v>26535</v>
+        <v>26120</v>
       </c>
       <c r="AH76" t="n">
-        <v>26620</v>
+        <v>26595</v>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
@@ -10582,13 +10582,13 @@
         </is>
       </c>
       <c r="AK76" t="n">
-        <v>26620</v>
+        <v>26595</v>
       </c>
       <c r="AL76" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.056316876290595</v>
+        <v>0.1501783367749202</v>
       </c>
       <c r="AN76" t="b">
         <v>0</v>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="AF77" t="n">
-        <v>465.45</v>
+        <v>462.25</v>
       </c>
       <c r="AG77" t="n">
-        <v>457.6</v>
+        <v>445.3</v>
       </c>
       <c r="AH77" t="n">
-        <v>457.6</v>
+        <v>446.35</v>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
@@ -10714,13 +10714,13 @@
         </is>
       </c>
       <c r="AK77" t="n">
-        <v>457.6</v>
+        <v>446.35</v>
       </c>
       <c r="AL77" t="n">
-        <v>0.1999999999999886</v>
+        <v>11.44999999999999</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0436871996504999</v>
+        <v>2.50109217999126</v>
       </c>
       <c r="AN77" t="b">
         <v>0</v>
@@ -10827,32 +10827,32 @@
         </is>
       </c>
       <c r="AF78" t="n">
-        <v>4009.8</v>
+        <v>4100.9</v>
       </c>
       <c r="AG78" t="n">
-        <v>3925</v>
+        <v>3915.1</v>
       </c>
       <c r="AH78" t="n">
-        <v>3970.6</v>
+        <v>4087.1</v>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK78" t="n">
-        <v>3970.6</v>
+        <v>4038.588</v>
       </c>
       <c r="AL78" t="n">
-        <v>-11.19999999999982</v>
+        <v>-79.1880000000001</v>
       </c>
       <c r="AM78" t="n">
-        <v>-0.2828711420922316</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AN78" t="b">
         <v>0</v>
@@ -10959,35 +10959,35 @@
         </is>
       </c>
       <c r="AF79" t="n">
-        <v>4334.9</v>
+        <v>4349</v>
       </c>
       <c r="AG79" t="n">
-        <v>4280</v>
+        <v>4136.1</v>
       </c>
       <c r="AH79" t="n">
-        <v>4294.3</v>
+        <v>4187.8</v>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>TARGET HIT</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Target reached during replay range</t>
         </is>
       </c>
       <c r="AK79" t="n">
-        <v>4294.3</v>
+        <v>4146.72</v>
       </c>
       <c r="AL79" t="n">
-        <v>25.19999999999981</v>
+        <v>172.7799999999998</v>
       </c>
       <c r="AM79" t="n">
-        <v>0.5834008565806186</v>
+        <v>3.999999999999994</v>
       </c>
       <c r="AN79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -11087,13 +11087,13 @@
         </is>
       </c>
       <c r="AF80" t="n">
-        <v>52.54</v>
+        <v>52.93</v>
       </c>
       <c r="AG80" t="n">
-        <v>52.01</v>
+        <v>52.08</v>
       </c>
       <c r="AH80" t="n">
-        <v>52.22</v>
+        <v>52.46</v>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
@@ -11106,13 +11106,13 @@
         </is>
       </c>
       <c r="AK80" t="n">
-        <v>52.22</v>
+        <v>52.46</v>
       </c>
       <c r="AL80" t="n">
-        <v>-0.0499999999999971</v>
+        <v>-0.2899999999999991</v>
       </c>
       <c r="AM80" t="n">
-        <v>-0.09584052137243081</v>
+        <v>-0.5558750239601287</v>
       </c>
       <c r="AN80" t="b">
         <v>0</v>
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="AF81" t="n">
-        <v>1905</v>
+        <v>1915.3</v>
       </c>
       <c r="AG81" t="n">
-        <v>1889.3</v>
+        <v>1890.1</v>
       </c>
       <c r="AH81" t="n">
-        <v>1889.8</v>
+        <v>1910.8</v>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
@@ -11238,13 +11238,13 @@
         </is>
       </c>
       <c r="AK81" t="n">
-        <v>1889.8</v>
+        <v>1910.8</v>
       </c>
       <c r="AL81" t="n">
-        <v>0.6000000000001364</v>
+        <v>-20.39999999999986</v>
       </c>
       <c r="AM81" t="n">
-        <v>0.0317393144308155</v>
+        <v>-1.079136690647475</v>
       </c>
       <c r="AN81" t="b">
         <v>0</v>
@@ -11351,13 +11351,13 @@
         </is>
       </c>
       <c r="AF82" t="n">
-        <v>1045.9</v>
+        <v>1047.8</v>
       </c>
       <c r="AG82" t="n">
-        <v>1029.4</v>
+        <v>1024.3</v>
       </c>
       <c r="AH82" t="n">
-        <v>1033.4</v>
+        <v>1041</v>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="AK82" t="n">
-        <v>1033.4</v>
+        <v>1041</v>
       </c>
       <c r="AL82" t="n">
-        <v>0.7999999999999545</v>
+        <v>-6.799999999999955</v>
       </c>
       <c r="AM82" t="n">
-        <v>0.07735447689034559</v>
+        <v>-0.6575130535679709</v>
       </c>
       <c r="AN82" t="b">
         <v>0</v>
@@ -11483,32 +11483,32 @@
         </is>
       </c>
       <c r="AF83" t="n">
-        <v>1318.6</v>
+        <v>1342</v>
       </c>
       <c r="AG83" t="n">
-        <v>1294.5</v>
+        <v>1297.6</v>
       </c>
       <c r="AH83" t="n">
-        <v>1299.2</v>
+        <v>1335.1</v>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK83" t="n">
-        <v>1299.2</v>
+        <v>1326.816</v>
       </c>
       <c r="AL83" t="n">
-        <v>1.599999999999909</v>
+        <v>-26.01600000000008</v>
       </c>
       <c r="AM83" t="n">
-        <v>0.1230012300122931</v>
+        <v>-2.000000000000006</v>
       </c>
       <c r="AN83" t="b">
         <v>0</v>
@@ -11615,13 +11615,13 @@
         </is>
       </c>
       <c r="AF84" t="n">
-        <v>1702.3</v>
+        <v>1754.3</v>
       </c>
       <c r="AG84" t="n">
-        <v>1666.9</v>
+        <v>1675</v>
       </c>
       <c r="AH84" t="n">
-        <v>1667.7</v>
+        <v>1734.9</v>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
@@ -11747,13 +11747,13 @@
         </is>
       </c>
       <c r="AF85" t="n">
-        <v>2833.4</v>
+        <v>2841</v>
       </c>
       <c r="AG85" t="n">
-        <v>2801.5</v>
+        <v>2762.3</v>
       </c>
       <c r="AH85" t="n">
-        <v>2821.5</v>
+        <v>2788.8</v>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
@@ -11766,13 +11766,13 @@
         </is>
       </c>
       <c r="AK85" t="n">
-        <v>2821.5</v>
+        <v>2788.8</v>
       </c>
       <c r="AL85" t="n">
-        <v>3.199999999999818</v>
+        <v>35.89999999999964</v>
       </c>
       <c r="AM85" t="n">
-        <v>0.1132863666938017</v>
+        <v>1.270931426346148</v>
       </c>
       <c r="AN85" t="b">
         <v>0</v>
@@ -11879,13 +11879,13 @@
         </is>
       </c>
       <c r="AF86" t="n">
-        <v>1782</v>
+        <v>1795</v>
       </c>
       <c r="AG86" t="n">
-        <v>1760.5</v>
+        <v>1767.2</v>
       </c>
       <c r="AH86" t="n">
-        <v>1777.6</v>
+        <v>1780.5</v>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
@@ -11898,13 +11898,13 @@
         </is>
       </c>
       <c r="AK86" t="n">
-        <v>1777.6</v>
+        <v>1780.5</v>
       </c>
       <c r="AL86" t="n">
-        <v>1.100000000000136</v>
+        <v>-1.799999999999954</v>
       </c>
       <c r="AM86" t="n">
-        <v>0.0618429189857838</v>
+        <v>-0.1011975037949038</v>
       </c>
       <c r="AN86" t="b">
         <v>0</v>
@@ -12011,32 +12011,32 @@
         </is>
       </c>
       <c r="AF87" t="n">
-        <v>1258.5</v>
+        <v>1307</v>
       </c>
       <c r="AG87" t="n">
-        <v>1239.8</v>
+        <v>1243.6</v>
       </c>
       <c r="AH87" t="n">
-        <v>1255.2</v>
+        <v>1290.6</v>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK87" t="n">
-        <v>1255.2</v>
+        <v>1281.12</v>
       </c>
       <c r="AL87" t="n">
-        <v>0.7999999999999545</v>
+        <v>-25.11999999999989</v>
       </c>
       <c r="AM87" t="n">
-        <v>0.0636942675159199</v>
+        <v>-1.999999999999992</v>
       </c>
       <c r="AN87" t="b">
         <v>0</v>
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="AF88" t="n">
-        <v>1031.5</v>
+        <v>1037.6</v>
       </c>
       <c r="AG88" t="n">
-        <v>1021.4</v>
+        <v>1008</v>
       </c>
       <c r="AH88" t="n">
-        <v>1026.4</v>
+        <v>1020.2</v>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
@@ -12162,13 +12162,13 @@
         </is>
       </c>
       <c r="AK88" t="n">
-        <v>1026.4</v>
+        <v>1020.2</v>
       </c>
       <c r="AL88" t="n">
-        <v>-0.2000000000000454</v>
+        <v>6</v>
       </c>
       <c r="AM88" t="n">
-        <v>-0.019489378288837</v>
+        <v>0.5846813486649776</v>
       </c>
       <c r="AN88" t="b">
         <v>0</v>
@@ -12275,13 +12275,13 @@
         </is>
       </c>
       <c r="AF89" t="n">
-        <v>1272.6</v>
+        <v>1290.3</v>
       </c>
       <c r="AG89" t="n">
-        <v>1256.6</v>
+        <v>1261.8</v>
       </c>
       <c r="AH89" t="n">
-        <v>1265.8</v>
+        <v>1286.1</v>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
@@ -12294,13 +12294,13 @@
         </is>
       </c>
       <c r="AK89" t="n">
-        <v>1265.8</v>
+        <v>1286.1</v>
       </c>
       <c r="AL89" t="n">
-        <v>0</v>
+        <v>-20.29999999999995</v>
       </c>
       <c r="AM89" t="n">
-        <v>0</v>
+        <v>-1.603728867119605</v>
       </c>
       <c r="AN89" t="b">
         <v>0</v>
@@ -12407,32 +12407,32 @@
         </is>
       </c>
       <c r="AF90" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG90" t="n">
-        <v>280.1</v>
+        <v>277.5</v>
       </c>
       <c r="AH90" t="n">
-        <v>280.8</v>
+        <v>281.8</v>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK90" t="n">
-        <v>280.8</v>
+        <v>286.518</v>
       </c>
       <c r="AL90" t="n">
-        <v>0.09999999999996589</v>
+        <v>-5.617999999999995</v>
       </c>
       <c r="AM90" t="n">
-        <v>0.0355998576005574</v>
+        <v>-1.999999999999998</v>
       </c>
       <c r="AN90" t="b">
         <v>0</v>
@@ -12539,13 +12539,13 @@
         </is>
       </c>
       <c r="AF91" t="n">
-        <v>619.85</v>
+        <v>619.15</v>
       </c>
       <c r="AG91" t="n">
-        <v>615</v>
+        <v>603.1</v>
       </c>
       <c r="AH91" t="n">
-        <v>618.2</v>
+        <v>614</v>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
@@ -12558,13 +12558,13 @@
         </is>
       </c>
       <c r="AK91" t="n">
-        <v>618.2</v>
+        <v>614</v>
       </c>
       <c r="AL91" t="n">
-        <v>-0.2000000000000454</v>
+        <v>4</v>
       </c>
       <c r="AM91" t="n">
-        <v>-0.0323624595469329</v>
+        <v>0.6472491909385114</v>
       </c>
       <c r="AN91" t="b">
         <v>0</v>
@@ -12671,13 +12671,13 @@
         </is>
       </c>
       <c r="AF92" t="n">
-        <v>4584</v>
+        <v>4620.7</v>
       </c>
       <c r="AG92" t="n">
-        <v>4544.3</v>
+        <v>4525.2</v>
       </c>
       <c r="AH92" t="n">
-        <v>4550</v>
+        <v>4593.9</v>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
@@ -12690,13 +12690,13 @@
         </is>
       </c>
       <c r="AK92" t="n">
-        <v>4550</v>
+        <v>4593.9</v>
       </c>
       <c r="AL92" t="n">
-        <v>-1</v>
+        <v>-44.89999999999964</v>
       </c>
       <c r="AM92" t="n">
-        <v>-0.0219828533743679</v>
+        <v>-0.9870301165091148</v>
       </c>
       <c r="AN92" t="b">
         <v>0</v>
@@ -12803,32 +12803,32 @@
         </is>
       </c>
       <c r="AF93" t="n">
-        <v>263.75</v>
+        <v>267.3</v>
       </c>
       <c r="AG93" t="n">
-        <v>260.55</v>
+        <v>261.35</v>
       </c>
       <c r="AH93" t="n">
-        <v>261.5</v>
+        <v>265.85</v>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK93" t="n">
-        <v>261.5</v>
+        <v>266.934</v>
       </c>
       <c r="AL93" t="n">
-        <v>0.1999999999999886</v>
+        <v>-5.234000000000037</v>
       </c>
       <c r="AM93" t="n">
-        <v>0.07642338555597571</v>
+        <v>-2.000000000000014</v>
       </c>
       <c r="AN93" t="b">
         <v>0</v>
@@ -12935,13 +12935,13 @@
         </is>
       </c>
       <c r="AF94" t="n">
-        <v>5037.3</v>
+        <v>4967.4</v>
       </c>
       <c r="AG94" t="n">
-        <v>4998</v>
+        <v>4895.8</v>
       </c>
       <c r="AH94" t="n">
-        <v>5024.2</v>
+        <v>4910.2</v>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
@@ -12954,13 +12954,13 @@
         </is>
       </c>
       <c r="AK94" t="n">
-        <v>5024.2</v>
+        <v>4910.2</v>
       </c>
       <c r="AL94" t="n">
-        <v>-0.8999999999996362</v>
+        <v>113.1000000000004</v>
       </c>
       <c r="AM94" t="n">
-        <v>-0.017916509067737</v>
+        <v>2.251507972846543</v>
       </c>
       <c r="AN94" t="b">
         <v>0</v>
@@ -13063,32 +13063,32 @@
         </is>
       </c>
       <c r="AF95" t="n">
-        <v>168.35</v>
+        <v>172.63</v>
       </c>
       <c r="AG95" t="n">
-        <v>166.75</v>
+        <v>166.51</v>
       </c>
       <c r="AH95" t="n">
-        <v>168.01</v>
+        <v>171.38</v>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK95" t="n">
-        <v>168.01</v>
+        <v>171.3906</v>
       </c>
       <c r="AL95" t="n">
-        <v>0.0200000000000102</v>
+        <v>-3.360600000000005</v>
       </c>
       <c r="AM95" t="n">
-        <v>0.0119026364339762</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AN95" t="b">
         <v>0</v>
@@ -13195,13 +13195,13 @@
         </is>
       </c>
       <c r="AF96" t="n">
-        <v>383.4</v>
+        <v>385.5</v>
       </c>
       <c r="AG96" t="n">
-        <v>378.75</v>
+        <v>373.5</v>
       </c>
       <c r="AH96" t="n">
-        <v>379.1</v>
+        <v>383.75</v>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="AK96" t="n">
-        <v>379.1</v>
+        <v>383.75</v>
       </c>
       <c r="AL96" t="n">
-        <v>-0.3500000000000227</v>
+        <v>-5</v>
       </c>
       <c r="AM96" t="n">
-        <v>-0.0924092409240984</v>
+        <v>-1.32013201320132</v>
       </c>
       <c r="AN96" t="b">
         <v>0</v>
@@ -13327,13 +13327,13 @@
         </is>
       </c>
       <c r="AF97" t="n">
-        <v>40285</v>
+        <v>40495</v>
       </c>
       <c r="AG97" t="n">
-        <v>39855</v>
+        <v>39705</v>
       </c>
       <c r="AH97" t="n">
-        <v>40090</v>
+        <v>40320</v>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="AK97" t="n">
-        <v>40090</v>
+        <v>40320</v>
       </c>
       <c r="AL97" t="n">
-        <v>-65</v>
+        <v>-295</v>
       </c>
       <c r="AM97" t="n">
-        <v>-0.1623985009369144</v>
+        <v>-0.7370393504059962</v>
       </c>
       <c r="AN97" t="b">
         <v>0</v>
@@ -13459,13 +13459,13 @@
         </is>
       </c>
       <c r="AF98" t="n">
-        <v>502.75</v>
+        <v>506.5</v>
       </c>
       <c r="AG98" t="n">
-        <v>496.8</v>
+        <v>498.15</v>
       </c>
       <c r="AH98" t="n">
-        <v>498.65</v>
+        <v>503.95</v>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="AK98" t="n">
-        <v>498.65</v>
+        <v>503.95</v>
       </c>
       <c r="AL98" t="n">
-        <v>-0.2999999999999545</v>
+        <v>-5.599999999999966</v>
       </c>
       <c r="AM98" t="n">
-        <v>-0.0601986555633499</v>
+        <v>-1.123708237182696</v>
       </c>
       <c r="AN98" t="b">
         <v>0</v>
@@ -13591,13 +13591,13 @@
         </is>
       </c>
       <c r="AF99" t="n">
-        <v>1419.7</v>
+        <v>1425</v>
       </c>
       <c r="AG99" t="n">
-        <v>1404.1</v>
+        <v>1369.4</v>
       </c>
       <c r="AH99" t="n">
-        <v>1413.1</v>
+        <v>1417.3</v>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="AK99" t="n">
-        <v>1413.1</v>
+        <v>1417.3</v>
       </c>
       <c r="AL99" t="n">
-        <v>-3.099999999999909</v>
+        <v>-7.299999999999954</v>
       </c>
       <c r="AM99" t="n">
-        <v>-0.2198581560283623</v>
+        <v>-0.5177304964538975</v>
       </c>
       <c r="AN99" t="b">
         <v>0</v>
@@ -13723,13 +13723,13 @@
         </is>
       </c>
       <c r="AF100" t="n">
-        <v>139</v>
+        <v>139.01</v>
       </c>
       <c r="AG100" t="n">
-        <v>137.68</v>
+        <v>136.2</v>
       </c>
       <c r="AH100" t="n">
-        <v>137.86</v>
+        <v>138.18</v>
       </c>
       <c r="AI100" t="inlineStr">
         <is>
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="AK100" t="n">
-        <v>137.86</v>
+        <v>138.18</v>
       </c>
       <c r="AL100" t="n">
-        <v>-0.0600000000000022</v>
+        <v>-0.3799999999999954</v>
       </c>
       <c r="AM100" t="n">
-        <v>-0.0435413642960829</v>
+        <v>-0.2757619738751781</v>
       </c>
       <c r="AN100" t="b">
         <v>0</v>
@@ -13851,13 +13851,13 @@
         </is>
       </c>
       <c r="AF101" t="n">
-        <v>87.11</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="AG101" t="n">
-        <v>86.22</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="AH101" t="n">
-        <v>86.55</v>
+        <v>86.56</v>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
@@ -13870,13 +13870,13 @@
         </is>
       </c>
       <c r="AK101" t="n">
-        <v>86.55</v>
+        <v>86.56</v>
       </c>
       <c r="AL101" t="n">
-        <v>-0.1299999999999954</v>
+        <v>-0.1400000000000005</v>
       </c>
       <c r="AM101" t="n">
-        <v>-0.1504281416338757</v>
+        <v>-0.1619995371441802</v>
       </c>
       <c r="AN101" t="b">
         <v>0</v>
@@ -13983,13 +13983,13 @@
         </is>
       </c>
       <c r="AF102" t="n">
-        <v>2868.7</v>
+        <v>2907</v>
       </c>
       <c r="AG102" t="n">
-        <v>2844.1</v>
+        <v>2824.7</v>
       </c>
       <c r="AH102" t="n">
-        <v>2853.4</v>
+        <v>2882.9</v>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
@@ -14002,13 +14002,13 @@
         </is>
       </c>
       <c r="AK102" t="n">
-        <v>2853.4</v>
+        <v>2882.9</v>
       </c>
       <c r="AL102" t="n">
-        <v>-2.700000000000273</v>
+        <v>-32.20000000000027</v>
       </c>
       <c r="AM102" t="n">
-        <v>-0.0947135791209272</v>
+        <v>-1.129547128775398</v>
       </c>
       <c r="AN102" t="b">
         <v>0</v>
@@ -14115,13 +14115,13 @@
         </is>
       </c>
       <c r="AF103" t="n">
-        <v>376.15</v>
+        <v>378</v>
       </c>
       <c r="AG103" t="n">
-        <v>373.5</v>
+        <v>373.15</v>
       </c>
       <c r="AH103" t="n">
-        <v>374.25</v>
+        <v>376.6</v>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
@@ -14134,13 +14134,13 @@
         </is>
       </c>
       <c r="AK103" t="n">
-        <v>374.25</v>
+        <v>376.6</v>
       </c>
       <c r="AL103" t="n">
-        <v>-0.3000000000000113</v>
+        <v>-2.650000000000034</v>
       </c>
       <c r="AM103" t="n">
-        <v>-0.0802246289610941</v>
+        <v>-0.7086508891563135</v>
       </c>
       <c r="AN103" t="b">
         <v>0</v>
@@ -14247,32 +14247,32 @@
         </is>
       </c>
       <c r="AF104" t="n">
-        <v>3440.8</v>
+        <v>3522</v>
       </c>
       <c r="AG104" t="n">
-        <v>3386.8</v>
+        <v>3402.3</v>
       </c>
       <c r="AH104" t="n">
-        <v>3410.6</v>
+        <v>3483.4</v>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK104" t="n">
-        <v>3410.6</v>
+        <v>3473.1</v>
       </c>
       <c r="AL104" t="n">
-        <v>-5.599999999999909</v>
+        <v>-68.09999999999991</v>
       </c>
       <c r="AM104" t="n">
-        <v>-0.1644640234948578</v>
+        <v>-1.999999999999997</v>
       </c>
       <c r="AN104" t="b">
         <v>0</v>
@@ -14379,13 +14379,13 @@
         </is>
       </c>
       <c r="AF105" t="n">
-        <v>1011.7</v>
+        <v>1024.1</v>
       </c>
       <c r="AG105" t="n">
-        <v>1003.2</v>
+        <v>1007.2</v>
       </c>
       <c r="AH105" t="n">
-        <v>1007.8</v>
+        <v>1021.8</v>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
@@ -14398,13 +14398,13 @@
         </is>
       </c>
       <c r="AK105" t="n">
-        <v>1007.8</v>
+        <v>1021.8</v>
       </c>
       <c r="AL105" t="n">
-        <v>0.2000000000000454</v>
+        <v>-13.79999999999996</v>
       </c>
       <c r="AM105" t="n">
-        <v>0.0198412698412743</v>
+        <v>-1.369047619047615</v>
       </c>
       <c r="AN105" t="b">
         <v>0</v>
@@ -14511,13 +14511,13 @@
         </is>
       </c>
       <c r="AF106" t="n">
-        <v>7664.5</v>
+        <v>7694</v>
       </c>
       <c r="AG106" t="n">
-        <v>7605.5</v>
+        <v>7528</v>
       </c>
       <c r="AH106" t="n">
-        <v>7605.5</v>
+        <v>7582.5</v>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
@@ -14530,13 +14530,13 @@
         </is>
       </c>
       <c r="AK106" t="n">
-        <v>7605.5</v>
+        <v>7582.5</v>
       </c>
       <c r="AL106" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AM106" t="n">
-        <v>0.0131466508906855</v>
+        <v>0.3155196213764544</v>
       </c>
       <c r="AN106" t="b">
         <v>0</v>
@@ -14643,13 +14643,13 @@
         </is>
       </c>
       <c r="AF107" t="n">
-        <v>5100</v>
+        <v>5113.9</v>
       </c>
       <c r="AG107" t="n">
-        <v>5030.9</v>
+        <v>5005.1</v>
       </c>
       <c r="AH107" t="n">
-        <v>5035.3</v>
+        <v>5032</v>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
@@ -14662,13 +14662,13 @@
         </is>
       </c>
       <c r="AK107" t="n">
-        <v>5035.3</v>
+        <v>5032</v>
       </c>
       <c r="AL107" t="n">
-        <v>-0.1999999999998181</v>
+        <v>3.100000000000364</v>
       </c>
       <c r="AM107" t="n">
-        <v>-0.0039721157474492</v>
+        <v>0.0615677940855268</v>
       </c>
       <c r="AN107" t="b">
         <v>0</v>
@@ -14775,13 +14775,13 @@
         </is>
       </c>
       <c r="AF108" t="n">
-        <v>1400.1</v>
+        <v>1397.4</v>
       </c>
       <c r="AG108" t="n">
-        <v>1370</v>
+        <v>1370.2</v>
       </c>
       <c r="AH108" t="n">
-        <v>1388.5</v>
+        <v>1383.3</v>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
@@ -14794,13 +14794,13 @@
         </is>
       </c>
       <c r="AK108" t="n">
-        <v>1388.5</v>
+        <v>1383.3</v>
       </c>
       <c r="AL108" t="n">
-        <v>0</v>
+        <v>5.200000000000045</v>
       </c>
       <c r="AM108" t="n">
-        <v>0</v>
+        <v>0.3745048613611844</v>
       </c>
       <c r="AN108" t="b">
         <v>0</v>
@@ -14907,32 +14907,32 @@
         </is>
       </c>
       <c r="AF109" t="n">
-        <v>978.5</v>
+        <v>1020</v>
       </c>
       <c r="AG109" t="n">
-        <v>968.2</v>
+        <v>972</v>
       </c>
       <c r="AH109" t="n">
-        <v>971.4</v>
+        <v>1010.8</v>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK109" t="n">
-        <v>971.4</v>
+        <v>990.624</v>
       </c>
       <c r="AL109" t="n">
-        <v>-0.1999999999999318</v>
+        <v>-19.42399999999997</v>
       </c>
       <c r="AM109" t="n">
-        <v>-0.0205930807248694</v>
+        <v>-1.999999999999998</v>
       </c>
       <c r="AN109" t="b">
         <v>0</v>
@@ -15039,13 +15039,13 @@
         </is>
       </c>
       <c r="AF110" t="n">
-        <v>11253.5</v>
+        <v>11378</v>
       </c>
       <c r="AG110" t="n">
-        <v>11190</v>
+        <v>11200</v>
       </c>
       <c r="AH110" t="n">
-        <v>11204.5</v>
+        <v>11212</v>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="AK110" t="n">
-        <v>11204.5</v>
+        <v>11212</v>
       </c>
       <c r="AL110" t="n">
-        <v>3</v>
+        <v>-4.5</v>
       </c>
       <c r="AM110" t="n">
-        <v>0.0267677894267231</v>
+        <v>-0.0401516841400847</v>
       </c>
       <c r="AN110" t="b">
         <v>0</v>
@@ -15171,13 +15171,13 @@
         </is>
       </c>
       <c r="AF111" t="n">
-        <v>109.11</v>
+        <v>109.8</v>
       </c>
       <c r="AG111" t="n">
-        <v>107.3</v>
+        <v>107</v>
       </c>
       <c r="AH111" t="n">
-        <v>107.8</v>
+        <v>108.01</v>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
@@ -15190,13 +15190,13 @@
         </is>
       </c>
       <c r="AK111" t="n">
-        <v>107.8</v>
+        <v>108.01</v>
       </c>
       <c r="AL111" t="n">
-        <v>-0.0499999999999971</v>
+        <v>-0.2600000000000051</v>
       </c>
       <c r="AM111" t="n">
-        <v>-0.0464037122969811</v>
+        <v>-0.2412993039443203</v>
       </c>
       <c r="AN111" t="b">
         <v>0</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="AF112" t="n">
-        <v>4685</v>
+        <v>4725.8</v>
       </c>
       <c r="AG112" t="n">
-        <v>4623.6</v>
+        <v>4675</v>
       </c>
       <c r="AH112" t="n">
-        <v>4659.9</v>
+        <v>4709.7</v>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
@@ -15322,13 +15322,13 @@
         </is>
       </c>
       <c r="AK112" t="n">
-        <v>4659.9</v>
+        <v>4709.7</v>
       </c>
       <c r="AL112" t="n">
-        <v>6.5</v>
+        <v>-43.30000000000018</v>
       </c>
       <c r="AM112" t="n">
-        <v>0.1392936739242242</v>
+        <v>-0.9279101662952208</v>
       </c>
       <c r="AN112" t="b">
         <v>0</v>
@@ -15435,13 +15435,13 @@
         </is>
       </c>
       <c r="AF113" t="n">
-        <v>2659.9</v>
+        <v>2675.7</v>
       </c>
       <c r="AG113" t="n">
-        <v>2640</v>
+        <v>2644.9</v>
       </c>
       <c r="AH113" t="n">
-        <v>2644</v>
+        <v>2657.2</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
@@ -15454,13 +15454,13 @@
         </is>
       </c>
       <c r="AK113" t="n">
-        <v>2644</v>
+        <v>2657.2</v>
       </c>
       <c r="AL113" t="n">
-        <v>2.599999999999909</v>
+        <v>-10.59999999999991</v>
       </c>
       <c r="AM113" t="n">
-        <v>0.09823925035894759</v>
+        <v>-0.400513866848028</v>
       </c>
       <c r="AN113" t="b">
         <v>0</v>
@@ -15567,32 +15567,32 @@
         </is>
       </c>
       <c r="AF114" t="n">
-        <v>2026.4</v>
+        <v>2048.8</v>
       </c>
       <c r="AG114" t="n">
-        <v>2000.4</v>
+        <v>2002.4</v>
       </c>
       <c r="AH114" t="n">
-        <v>2001</v>
+        <v>2030</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK114" t="n">
-        <v>2001</v>
+        <v>2040</v>
       </c>
       <c r="AL114" t="n">
-        <v>-1</v>
+        <v>-40</v>
       </c>
       <c r="AM114" t="n">
-        <v>-0.05</v>
+        <v>-2</v>
       </c>
       <c r="AN114" t="b">
         <v>0</v>
@@ -15699,13 +15699,13 @@
         </is>
       </c>
       <c r="AF115" t="n">
-        <v>18543</v>
+        <v>18740</v>
       </c>
       <c r="AG115" t="n">
-        <v>18201</v>
+        <v>18400</v>
       </c>
       <c r="AH115" t="n">
-        <v>18514</v>
+        <v>18607</v>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="AK115" t="n">
-        <v>18514</v>
+        <v>18607</v>
       </c>
       <c r="AL115" t="n">
-        <v>-25</v>
+        <v>-118</v>
       </c>
       <c r="AM115" t="n">
-        <v>-0.1352155335604954</v>
+        <v>-0.6382173184055384</v>
       </c>
       <c r="AN115" t="b">
         <v>0</v>
@@ -15831,13 +15831,13 @@
         </is>
       </c>
       <c r="AF116" t="n">
-        <v>119.42</v>
+        <v>116.74</v>
       </c>
       <c r="AG116" t="n">
-        <v>118.36</v>
+        <v>114.13</v>
       </c>
       <c r="AH116" t="n">
-        <v>118.5</v>
+        <v>116.11</v>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
@@ -15850,13 +15850,13 @@
         </is>
       </c>
       <c r="AK116" t="n">
-        <v>118.5</v>
+        <v>116.11</v>
       </c>
       <c r="AL116" t="n">
-        <v>-0.2000000000000028</v>
+        <v>2.189999999999998</v>
       </c>
       <c r="AM116" t="n">
-        <v>-0.1690617075232484</v>
+        <v>1.851225697379542</v>
       </c>
       <c r="AN116" t="b">
         <v>0</v>
@@ -15963,13 +15963,13 @@
         </is>
       </c>
       <c r="AF117" t="n">
-        <v>2220</v>
+        <v>2218.2</v>
       </c>
       <c r="AG117" t="n">
-        <v>2182</v>
+        <v>2190.7</v>
       </c>
       <c r="AH117" t="n">
-        <v>2199.6</v>
+        <v>2205.3</v>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="AK117" t="n">
-        <v>2199.6</v>
+        <v>2205.3</v>
       </c>
       <c r="AL117" t="n">
-        <v>-2.599999999999909</v>
+        <v>-8.300000000000182</v>
       </c>
       <c r="AM117" t="n">
-        <v>-0.118343195266268</v>
+        <v>-0.3777878925808003</v>
       </c>
       <c r="AN117" t="b">
         <v>0</v>
@@ -16095,13 +16095,13 @@
         </is>
       </c>
       <c r="AF118" t="n">
-        <v>108.08</v>
+        <v>108.06</v>
       </c>
       <c r="AG118" t="n">
-        <v>105.76</v>
+        <v>106.17</v>
       </c>
       <c r="AH118" t="n">
-        <v>106.18</v>
+        <v>107.64</v>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
@@ -16114,13 +16114,13 @@
         </is>
       </c>
       <c r="AK118" t="n">
-        <v>106.18</v>
+        <v>107.64</v>
       </c>
       <c r="AL118" t="n">
-        <v>0.0999999999999943</v>
+        <v>-1.359999999999999</v>
       </c>
       <c r="AM118" t="n">
-        <v>0.09409108016559491</v>
+        <v>-1.279638690252164</v>
       </c>
       <c r="AN118" t="b">
         <v>0</v>
@@ -16227,13 +16227,13 @@
         </is>
       </c>
       <c r="AF119" t="n">
-        <v>1822.8</v>
+        <v>1841.6</v>
       </c>
       <c r="AG119" t="n">
-        <v>1804.2</v>
+        <v>1808.4</v>
       </c>
       <c r="AH119" t="n">
-        <v>1811.6</v>
+        <v>1833.4</v>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="AK119" t="n">
-        <v>1811.6</v>
+        <v>1833.4</v>
       </c>
       <c r="AL119" t="n">
-        <v>1.100000000000136</v>
+        <v>-20.70000000000005</v>
       </c>
       <c r="AM119" t="n">
-        <v>0.0606829591217596</v>
+        <v>-1.141942958018428</v>
       </c>
       <c r="AN119" t="b">
         <v>0</v>
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="AF120" t="n">
-        <v>1431.3</v>
+        <v>1435.6</v>
       </c>
       <c r="AG120" t="n">
-        <v>1421.8</v>
+        <v>1414.2</v>
       </c>
       <c r="AH120" t="n">
-        <v>1424.1</v>
+        <v>1428.1</v>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
@@ -16378,13 +16378,13 @@
         </is>
       </c>
       <c r="AK120" t="n">
-        <v>1424.1</v>
+        <v>1428.1</v>
       </c>
       <c r="AL120" t="n">
-        <v>0.2000000000000454</v>
+        <v>-3.799999999999955</v>
       </c>
       <c r="AM120" t="n">
-        <v>0.014041985536758</v>
+        <v>-0.2667977251983399</v>
       </c>
       <c r="AN120" t="b">
         <v>0</v>
@@ -16491,32 +16491,32 @@
         </is>
       </c>
       <c r="AF121" t="n">
-        <v>150.5</v>
+        <v>152.36</v>
       </c>
       <c r="AG121" t="n">
-        <v>148.34</v>
+        <v>148.14</v>
       </c>
       <c r="AH121" t="n">
-        <v>148.83</v>
+        <v>152.15</v>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK121" t="n">
-        <v>148.83</v>
+        <v>151.674</v>
       </c>
       <c r="AL121" t="n">
-        <v>-0.1300000000000238</v>
+        <v>-2.973999999999989</v>
       </c>
       <c r="AM121" t="n">
-        <v>-0.08742434431743359</v>
+        <v>-1.999999999999993</v>
       </c>
       <c r="AN121" t="b">
         <v>0</v>
@@ -16619,13 +16619,13 @@
         </is>
       </c>
       <c r="AF122" t="n">
-        <v>109.7</v>
+        <v>111.41</v>
       </c>
       <c r="AG122" t="n">
-        <v>108.55</v>
+        <v>109.43</v>
       </c>
       <c r="AH122" t="n">
-        <v>109.49</v>
+        <v>111.14</v>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
@@ -16638,13 +16638,13 @@
         </is>
       </c>
       <c r="AK122" t="n">
-        <v>109.49</v>
+        <v>111.14</v>
       </c>
       <c r="AL122" t="n">
-        <v>-0.039999999999992</v>
+        <v>-1.689999999999998</v>
       </c>
       <c r="AM122" t="n">
-        <v>-0.0365463682046523</v>
+        <v>-1.544084056646868</v>
       </c>
       <c r="AN122" t="b">
         <v>0</v>
@@ -16751,32 +16751,32 @@
         </is>
       </c>
       <c r="AF123" t="n">
-        <v>409</v>
+        <v>420.5</v>
       </c>
       <c r="AG123" t="n">
-        <v>403.6</v>
+        <v>404.75</v>
       </c>
       <c r="AH123" t="n">
-        <v>406.6</v>
+        <v>419.55</v>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK123" t="n">
-        <v>406.6</v>
+        <v>414.069</v>
       </c>
       <c r="AL123" t="n">
-        <v>-0.6500000000000341</v>
+        <v>-8.119000000000028</v>
       </c>
       <c r="AM123" t="n">
-        <v>-0.1601182411627131</v>
+        <v>-2.000000000000007</v>
       </c>
       <c r="AN123" t="b">
         <v>0</v>
@@ -16883,13 +16883,13 @@
         </is>
       </c>
       <c r="AF124" t="n">
-        <v>183.11</v>
+        <v>184.75</v>
       </c>
       <c r="AG124" t="n">
-        <v>181.5</v>
+        <v>182.1</v>
       </c>
       <c r="AH124" t="n">
-        <v>181.98</v>
+        <v>183.98</v>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
@@ -16902,13 +16902,13 @@
         </is>
       </c>
       <c r="AK124" t="n">
-        <v>181.98</v>
+        <v>183.98</v>
       </c>
       <c r="AL124" t="n">
-        <v>0.0400000000000204</v>
+        <v>-1.95999999999998</v>
       </c>
       <c r="AM124" t="n">
-        <v>0.0219756070761567</v>
+        <v>-1.076804746731117</v>
       </c>
       <c r="AN124" t="b">
         <v>0</v>
@@ -17015,13 +17015,13 @@
         </is>
       </c>
       <c r="AF125" t="n">
-        <v>824.95</v>
+        <v>833.05</v>
       </c>
       <c r="AG125" t="n">
-        <v>816</v>
+        <v>816.05</v>
       </c>
       <c r="AH125" t="n">
-        <v>819.45</v>
+        <v>828.8</v>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
@@ -17034,13 +17034,13 @@
         </is>
       </c>
       <c r="AK125" t="n">
-        <v>819.45</v>
+        <v>828.8</v>
       </c>
       <c r="AL125" t="n">
-        <v>-0.6500000000000909</v>
+        <v>-10</v>
       </c>
       <c r="AM125" t="n">
-        <v>-0.0793844650708464</v>
+        <v>-1.221299462628236</v>
       </c>
       <c r="AN125" t="b">
         <v>0</v>
@@ -17147,13 +17147,13 @@
         </is>
       </c>
       <c r="AF126" t="n">
-        <v>349</v>
+        <v>351.25</v>
       </c>
       <c r="AG126" t="n">
-        <v>345.5</v>
+        <v>346.45</v>
       </c>
       <c r="AH126" t="n">
-        <v>346.5</v>
+        <v>349.1</v>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
@@ -17166,13 +17166,13 @@
         </is>
       </c>
       <c r="AK126" t="n">
-        <v>346.5</v>
+        <v>349.1</v>
       </c>
       <c r="AL126" t="n">
-        <v>-0.0500000000000113</v>
+        <v>-2.650000000000034</v>
       </c>
       <c r="AM126" t="n">
-        <v>-0.014432096983695</v>
+        <v>-0.7649011401356716</v>
       </c>
       <c r="AN126" t="b">
         <v>0</v>
@@ -17279,32 +17279,32 @@
         </is>
       </c>
       <c r="AF127" t="n">
-        <v>562.05</v>
+        <v>558.9</v>
       </c>
       <c r="AG127" t="n">
-        <v>549.6</v>
+        <v>548.95</v>
       </c>
       <c r="AH127" t="n">
-        <v>549.95</v>
+        <v>555.15</v>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>STOP LOSS HIT</t>
+          <t>EOD EXIT</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>Stop loss breached during replay range</t>
+          <t>Neither target nor stop reached; exited at close</t>
         </is>
       </c>
       <c r="AK127" t="n">
-        <v>561.7140000000001</v>
+        <v>555.15</v>
       </c>
       <c r="AL127" t="n">
-        <v>-11.01400000000001</v>
+        <v>-4.449999999999932</v>
       </c>
       <c r="AM127" t="n">
-        <v>-2.000000000000002</v>
+        <v>-0.8080624659524117</v>
       </c>
       <c r="AN127" t="b">
         <v>0</v>
@@ -17411,13 +17411,13 @@
         </is>
       </c>
       <c r="AF128" t="n">
-        <v>3898.9</v>
+        <v>3916</v>
       </c>
       <c r="AG128" t="n">
-        <v>3832.6</v>
+        <v>3846.3</v>
       </c>
       <c r="AH128" t="n">
-        <v>3879.9</v>
+        <v>3883.5</v>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
@@ -17430,13 +17430,13 @@
         </is>
       </c>
       <c r="AK128" t="n">
-        <v>3879.9</v>
+        <v>3883.5</v>
       </c>
       <c r="AL128" t="n">
-        <v>-0.099999999999909</v>
+        <v>-3.699999999999818</v>
       </c>
       <c r="AM128" t="n">
-        <v>-0.002577452446</v>
+        <v>-0.095365740502083</v>
       </c>
       <c r="AN128" t="b">
         <v>0</v>
@@ -17539,13 +17539,13 @@
         </is>
       </c>
       <c r="AF129" t="n">
-        <v>171.29</v>
+        <v>172</v>
       </c>
       <c r="AG129" t="n">
-        <v>170.2</v>
+        <v>167.67</v>
       </c>
       <c r="AH129" t="n">
-        <v>171.29</v>
+        <v>170.66</v>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
@@ -17558,13 +17558,13 @@
         </is>
       </c>
       <c r="AK129" t="n">
-        <v>171.29</v>
+        <v>170.66</v>
       </c>
       <c r="AL129" t="n">
-        <v>-0.2999999999999829</v>
+        <v>0.3300000000000125</v>
       </c>
       <c r="AM129" t="n">
-        <v>-0.1754488566582741</v>
+        <v>0.1929937423241198</v>
       </c>
       <c r="AN129" t="b">
         <v>0</v>
@@ -17671,13 +17671,13 @@
         </is>
       </c>
       <c r="AF130" t="n">
-        <v>71500.2</v>
+        <v>72199.8</v>
       </c>
       <c r="AG130" t="n">
-        <v>71066.39999999999</v>
+        <v>71400</v>
       </c>
       <c r="AH130" t="n">
-        <v>71317.2</v>
+        <v>72094.2</v>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
@@ -17690,13 +17690,13 @@
         </is>
       </c>
       <c r="AK130" t="n">
-        <v>71317.2</v>
+        <v>72094.2</v>
       </c>
       <c r="AL130" t="n">
-        <v>0</v>
+        <v>-777</v>
       </c>
       <c r="AM130" t="n">
-        <v>0</v>
+        <v>-1.089498746445458</v>
       </c>
       <c r="AN130" t="b">
         <v>0</v>
@@ -17803,13 +17803,13 @@
         </is>
       </c>
       <c r="AF131" t="n">
-        <v>2177.9</v>
+        <v>2181.5</v>
       </c>
       <c r="AG131" t="n">
-        <v>2153.4</v>
+        <v>2142.2</v>
       </c>
       <c r="AH131" t="n">
-        <v>2157.6</v>
+        <v>2165.8</v>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
@@ -17822,13 +17822,13 @@
         </is>
       </c>
       <c r="AK131" t="n">
-        <v>2157.6</v>
+        <v>2165.8</v>
       </c>
       <c r="AL131" t="n">
-        <v>-1.699999999999818</v>
+        <v>-9.900000000000093</v>
       </c>
       <c r="AM131" t="n">
-        <v>-0.0788533790992076</v>
+        <v>-0.4592049724013214</v>
       </c>
       <c r="AN131" t="b">
         <v>0</v>
@@ -17931,13 +17931,13 @@
         </is>
       </c>
       <c r="AF132" t="n">
-        <v>289.75</v>
+        <v>290.8</v>
       </c>
       <c r="AG132" t="n">
-        <v>286.2</v>
+        <v>287.55</v>
       </c>
       <c r="AH132" t="n">
-        <v>289</v>
+        <v>289.25</v>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
@@ -17950,13 +17950,13 @@
         </is>
       </c>
       <c r="AK132" t="n">
-        <v>289</v>
+        <v>289.25</v>
       </c>
       <c r="AL132" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="AM132" t="n">
-        <v>0</v>
+        <v>-0.08650519031141859</v>
       </c>
       <c r="AN132" t="b">
         <v>0</v>
@@ -18063,13 +18063,13 @@
         </is>
       </c>
       <c r="AF133" t="n">
-        <v>383.65</v>
+        <v>389.2</v>
       </c>
       <c r="AG133" t="n">
-        <v>380</v>
+        <v>381.6</v>
       </c>
       <c r="AH133" t="n">
-        <v>383.1</v>
+        <v>387.5</v>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
@@ -18082,13 +18082,13 @@
         </is>
       </c>
       <c r="AK133" t="n">
-        <v>383.1</v>
+        <v>387.5</v>
       </c>
       <c r="AL133" t="n">
-        <v>-0.3500000000000227</v>
+        <v>-4.75</v>
       </c>
       <c r="AM133" t="n">
-        <v>-0.0914435009797577</v>
+        <v>-1.24101894186806</v>
       </c>
       <c r="AN133" t="b">
         <v>0</v>
@@ -18195,13 +18195,13 @@
         </is>
       </c>
       <c r="AF134" t="n">
-        <v>414.3</v>
+        <v>417.5</v>
       </c>
       <c r="AG134" t="n">
-        <v>410.45</v>
+        <v>408.25</v>
       </c>
       <c r="AH134" t="n">
-        <v>412.4</v>
+        <v>416.4</v>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
@@ -18214,13 +18214,13 @@
         </is>
       </c>
       <c r="AK134" t="n">
-        <v>412.4</v>
+        <v>416.4</v>
       </c>
       <c r="AL134" t="n">
-        <v>0.1000000000000227</v>
+        <v>-3.899999999999977</v>
       </c>
       <c r="AM134" t="n">
-        <v>0.0242424242424297</v>
+        <v>-0.94545454545454</v>
       </c>
       <c r="AN134" t="b">
         <v>0</v>
@@ -18327,13 +18327,13 @@
         </is>
       </c>
       <c r="AF135" t="n">
-        <v>3215</v>
+        <v>3235.1</v>
       </c>
       <c r="AG135" t="n">
-        <v>3182</v>
+        <v>3151</v>
       </c>
       <c r="AH135" t="n">
-        <v>3182</v>
+        <v>3174.9</v>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
@@ -18346,13 +18346,13 @@
         </is>
       </c>
       <c r="AK135" t="n">
-        <v>3182</v>
+        <v>3174.9</v>
       </c>
       <c r="AL135" t="n">
-        <v>0.099999999999909</v>
+        <v>7.199999999999818</v>
       </c>
       <c r="AM135" t="n">
-        <v>0.0031425788001605</v>
+        <v>0.2262656736117601</v>
       </c>
       <c r="AN135" t="b">
         <v>0</v>
@@ -18459,32 +18459,32 @@
         </is>
       </c>
       <c r="AF136" t="n">
-        <v>1123.4</v>
+        <v>1136.3</v>
       </c>
       <c r="AG136" t="n">
-        <v>1112.4</v>
+        <v>1105.1</v>
       </c>
       <c r="AH136" t="n">
-        <v>1112.7</v>
+        <v>1130.8</v>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK136" t="n">
-        <v>1112.7</v>
+        <v>1132.302</v>
       </c>
       <c r="AL136" t="n">
-        <v>-2.600000000000136</v>
+        <v>-22.202</v>
       </c>
       <c r="AM136" t="n">
-        <v>-0.2342131339519085</v>
+        <v>-2</v>
       </c>
       <c r="AN136" t="b">
         <v>0</v>
@@ -18591,13 +18591,13 @@
         </is>
       </c>
       <c r="AF137" t="n">
-        <v>41990</v>
+        <v>41945</v>
       </c>
       <c r="AG137" t="n">
-        <v>41800</v>
+        <v>41440</v>
       </c>
       <c r="AH137" t="n">
-        <v>41895</v>
+        <v>41705</v>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
@@ -18610,13 +18610,13 @@
         </is>
       </c>
       <c r="AK137" t="n">
-        <v>41895</v>
+        <v>41705</v>
       </c>
       <c r="AL137" t="n">
-        <v>-135</v>
+        <v>55</v>
       </c>
       <c r="AM137" t="n">
-        <v>-0.3232758620689655</v>
+        <v>0.1317049808429118</v>
       </c>
       <c r="AN137" t="b">
         <v>0</v>
@@ -18723,13 +18723,13 @@
         </is>
       </c>
       <c r="AF138" t="n">
-        <v>745.85</v>
+        <v>753</v>
       </c>
       <c r="AG138" t="n">
-        <v>739.55</v>
+        <v>742.1</v>
       </c>
       <c r="AH138" t="n">
-        <v>741.2</v>
+        <v>748.1</v>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
@@ -18742,13 +18742,13 @@
         </is>
       </c>
       <c r="AK138" t="n">
-        <v>741.2</v>
+        <v>748.1</v>
       </c>
       <c r="AL138" t="n">
-        <v>0</v>
+        <v>-6.899999999999977</v>
       </c>
       <c r="AM138" t="n">
-        <v>0</v>
+        <v>-0.930922827846732</v>
       </c>
       <c r="AN138" t="b">
         <v>0</v>
@@ -18855,32 +18855,32 @@
         </is>
       </c>
       <c r="AF139" t="n">
-        <v>1503</v>
+        <v>1533</v>
       </c>
       <c r="AG139" t="n">
-        <v>1490.1</v>
+        <v>1493.6</v>
       </c>
       <c r="AH139" t="n">
-        <v>1495.4</v>
+        <v>1526.3</v>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK139" t="n">
-        <v>1495.4</v>
+        <v>1526.022</v>
       </c>
       <c r="AL139" t="n">
-        <v>0.6999999999998181</v>
+        <v>-29.92200000000003</v>
       </c>
       <c r="AM139" t="n">
-        <v>0.0467883162890059</v>
+        <v>-2.000000000000002</v>
       </c>
       <c r="AN139" t="b">
         <v>0</v>
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="AF140" t="n">
-        <v>2161.1</v>
+        <v>2175.4</v>
       </c>
       <c r="AG140" t="n">
-        <v>2145.4</v>
+        <v>2152.9</v>
       </c>
       <c r="AH140" t="n">
-        <v>2158.1</v>
+        <v>2157.7</v>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
@@ -19006,13 +19006,13 @@
         </is>
       </c>
       <c r="AK140" t="n">
-        <v>2158.1</v>
+        <v>2157.7</v>
       </c>
       <c r="AL140" t="n">
-        <v>-1.900000000000091</v>
+        <v>-1.5</v>
       </c>
       <c r="AM140" t="n">
-        <v>-0.08811798534459191</v>
+        <v>-0.0695668305352008</v>
       </c>
       <c r="AN140" t="b">
         <v>0</v>
@@ -19119,32 +19119,32 @@
         </is>
       </c>
       <c r="AF141" t="n">
-        <v>308.5</v>
+        <v>313.45</v>
       </c>
       <c r="AG141" t="n">
-        <v>305.7</v>
+        <v>307.25</v>
       </c>
       <c r="AH141" t="n">
-        <v>306.2</v>
+        <v>312.35</v>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK141" t="n">
-        <v>306.2</v>
+        <v>312.12</v>
       </c>
       <c r="AL141" t="n">
-        <v>-0.1999999999999886</v>
+        <v>-6.120000000000005</v>
       </c>
       <c r="AM141" t="n">
-        <v>-0.06535947712417919</v>
+        <v>-2.000000000000001</v>
       </c>
       <c r="AN141" t="b">
         <v>0</v>
@@ -19251,32 +19251,32 @@
         </is>
       </c>
       <c r="AF142" t="n">
-        <v>327.5</v>
+        <v>325.55</v>
       </c>
       <c r="AG142" t="n">
-        <v>320.45</v>
+        <v>319</v>
       </c>
       <c r="AH142" t="n">
-        <v>320.8</v>
+        <v>324.9</v>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>STOP LOSS HIT</t>
+          <t>EOD EXIT</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>Stop loss breached during replay range</t>
+          <t>Neither target nor stop reached; exited at close</t>
         </is>
       </c>
       <c r="AK142" t="n">
-        <v>327.216</v>
+        <v>324.9</v>
       </c>
       <c r="AL142" t="n">
-        <v>-6.415999999999997</v>
+        <v>-4.099999999999966</v>
       </c>
       <c r="AM142" t="n">
-        <v>-1.999999999999999</v>
+        <v>-1.278054862842882</v>
       </c>
       <c r="AN142" t="b">
         <v>0</v>
@@ -19383,13 +19383,13 @@
         </is>
       </c>
       <c r="AF143" t="n">
-        <v>303.35</v>
+        <v>302</v>
       </c>
       <c r="AG143" t="n">
-        <v>299.9</v>
+        <v>293.55</v>
       </c>
       <c r="AH143" t="n">
-        <v>300.5</v>
+        <v>299.6</v>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
@@ -19402,13 +19402,13 @@
         </is>
       </c>
       <c r="AK143" t="n">
-        <v>300.5</v>
+        <v>299.6</v>
       </c>
       <c r="AL143" t="n">
-        <v>0</v>
+        <v>0.8999999999999773</v>
       </c>
       <c r="AM143" t="n">
-        <v>0</v>
+        <v>0.2995008319467478</v>
       </c>
       <c r="AN143" t="b">
         <v>0</v>
@@ -19515,13 +19515,13 @@
         </is>
       </c>
       <c r="AF144" t="n">
-        <v>7309.5</v>
+        <v>7328</v>
       </c>
       <c r="AG144" t="n">
-        <v>7178.5</v>
+        <v>7225.5</v>
       </c>
       <c r="AH144" t="n">
-        <v>7278</v>
+        <v>7299</v>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
@@ -19534,13 +19534,13 @@
         </is>
       </c>
       <c r="AK144" t="n">
-        <v>7278</v>
+        <v>7299</v>
       </c>
       <c r="AL144" t="n">
-        <v>-6</v>
+        <v>-27</v>
       </c>
       <c r="AM144" t="n">
-        <v>-0.08250825082508249</v>
+        <v>-0.3712871287128713</v>
       </c>
       <c r="AN144" t="b">
         <v>0</v>
@@ -19647,13 +19647,13 @@
         </is>
       </c>
       <c r="AF145" t="n">
-        <v>1070.6</v>
+        <v>1068</v>
       </c>
       <c r="AG145" t="n">
-        <v>1054.4</v>
+        <v>1037</v>
       </c>
       <c r="AH145" t="n">
-        <v>1066.1</v>
+        <v>1056.4</v>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
@@ -19666,13 +19666,13 @@
         </is>
       </c>
       <c r="AK145" t="n">
-        <v>1066.1</v>
+        <v>1056.4</v>
       </c>
       <c r="AL145" t="n">
-        <v>-1.699999999999818</v>
+        <v>8</v>
       </c>
       <c r="AM145" t="n">
-        <v>-0.1597143930852891</v>
+        <v>0.7515971439308531</v>
       </c>
       <c r="AN145" t="b">
         <v>0</v>
@@ -19779,13 +19779,13 @@
         </is>
       </c>
       <c r="AF146" t="n">
-        <v>5588.5</v>
+        <v>5688</v>
       </c>
       <c r="AG146" t="n">
-        <v>5550</v>
+        <v>5570</v>
       </c>
       <c r="AH146" t="n">
-        <v>5588.5</v>
+        <v>5645</v>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
@@ -19798,13 +19798,13 @@
         </is>
       </c>
       <c r="AK146" t="n">
-        <v>5588.5</v>
+        <v>5645</v>
       </c>
       <c r="AL146" t="n">
-        <v>-7.5</v>
+        <v>-64</v>
       </c>
       <c r="AM146" t="n">
-        <v>-0.1343845189034223</v>
+        <v>-1.146747894642537</v>
       </c>
       <c r="AN146" t="b">
         <v>0</v>
@@ -19907,13 +19907,13 @@
         </is>
       </c>
       <c r="AF147" t="n">
-        <v>281.8</v>
+        <v>286.95</v>
       </c>
       <c r="AG147" t="n">
-        <v>280</v>
+        <v>281.55</v>
       </c>
       <c r="AH147" t="n">
-        <v>281.5</v>
+        <v>285.35</v>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
@@ -19926,13 +19926,13 @@
         </is>
       </c>
       <c r="AK147" t="n">
-        <v>281.5</v>
+        <v>285.35</v>
       </c>
       <c r="AL147" t="n">
-        <v>-0.1499999999999772</v>
+        <v>-4</v>
       </c>
       <c r="AM147" t="n">
-        <v>-0.0533143771103526</v>
+        <v>-1.421716722942954</v>
       </c>
       <c r="AN147" t="b">
         <v>0</v>
@@ -20035,32 +20035,32 @@
         </is>
       </c>
       <c r="AF148" t="n">
-        <v>79.68000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="AG148" t="n">
-        <v>79.14</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="AH148" t="n">
-        <v>79.39</v>
+        <v>81.23</v>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK148" t="n">
-        <v>79.39</v>
+        <v>80.77379999999999</v>
       </c>
       <c r="AL148" t="n">
-        <v>-0.2000000000000028</v>
+        <v>-1.583799999999996</v>
       </c>
       <c r="AM148" t="n">
-        <v>-0.2525571410531669</v>
+        <v>-1.999999999999996</v>
       </c>
       <c r="AN148" t="b">
         <v>0</v>
@@ -20167,32 +20167,32 @@
         </is>
       </c>
       <c r="AF149" t="n">
-        <v>338.55</v>
+        <v>345.35</v>
       </c>
       <c r="AG149" t="n">
-        <v>334.15</v>
+        <v>331.7</v>
       </c>
       <c r="AH149" t="n">
-        <v>336.6</v>
+        <v>342.95</v>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK149" t="n">
-        <v>336.6</v>
+        <v>342.414</v>
       </c>
       <c r="AL149" t="n">
-        <v>-0.9000000000000341</v>
+        <v>-6.713999999999999</v>
       </c>
       <c r="AM149" t="n">
-        <v>-0.2680965147453185</v>
+        <v>-2</v>
       </c>
       <c r="AN149" t="b">
         <v>0</v>
@@ -20299,13 +20299,13 @@
         </is>
       </c>
       <c r="AF150" t="n">
-        <v>421.95</v>
+        <v>427.75</v>
       </c>
       <c r="AG150" t="n">
-        <v>419.5</v>
+        <v>420.15</v>
       </c>
       <c r="AH150" t="n">
-        <v>421.5</v>
+        <v>425.2</v>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
@@ -20318,13 +20318,13 @@
         </is>
       </c>
       <c r="AK150" t="n">
-        <v>421.5</v>
+        <v>425.2</v>
       </c>
       <c r="AL150" t="n">
-        <v>-0.1999999999999886</v>
+        <v>-3.899999999999977</v>
       </c>
       <c r="AM150" t="n">
-        <v>-0.0474721101352928</v>
+        <v>-0.9257061476382572</v>
       </c>
       <c r="AN150" t="b">
         <v>0</v>
@@ -20431,13 +20431,13 @@
         </is>
       </c>
       <c r="AF151" t="n">
-        <v>1957.1</v>
+        <v>1949.7</v>
       </c>
       <c r="AG151" t="n">
-        <v>1925.1</v>
+        <v>1898.8</v>
       </c>
       <c r="AH151" t="n">
-        <v>1942.5</v>
+        <v>1923</v>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
@@ -20450,13 +20450,13 @@
         </is>
       </c>
       <c r="AK151" t="n">
-        <v>1942.5</v>
+        <v>1923</v>
       </c>
       <c r="AL151" t="n">
-        <v>0.2999999999999545</v>
+        <v>19.79999999999995</v>
       </c>
       <c r="AM151" t="n">
-        <v>0.0154416306361928</v>
+        <v>1.01914762198888</v>
       </c>
       <c r="AN151" t="b">
         <v>0</v>
@@ -20563,13 +20563,13 @@
         </is>
       </c>
       <c r="AF152" t="n">
-        <v>1081.7</v>
+        <v>1088.8</v>
       </c>
       <c r="AG152" t="n">
-        <v>1069.6</v>
+        <v>1072.9</v>
       </c>
       <c r="AH152" t="n">
-        <v>1077.4</v>
+        <v>1083.7</v>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
@@ -20582,13 +20582,13 @@
         </is>
       </c>
       <c r="AK152" t="n">
-        <v>1077.4</v>
+        <v>1083.7</v>
       </c>
       <c r="AL152" t="n">
-        <v>-0.6000000000001364</v>
+        <v>-6.900000000000091</v>
       </c>
       <c r="AM152" t="n">
-        <v>-0.0557206537890171</v>
+        <v>-0.6407875185735598</v>
       </c>
       <c r="AN152" t="b">
         <v>0</v>
@@ -20695,13 +20695,13 @@
         </is>
       </c>
       <c r="AF153" t="n">
-        <v>3674.8</v>
+        <v>3675</v>
       </c>
       <c r="AG153" t="n">
-        <v>3626.4</v>
+        <v>3568</v>
       </c>
       <c r="AH153" t="n">
-        <v>3633</v>
+        <v>3661.2</v>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
@@ -20714,13 +20714,13 @@
         </is>
       </c>
       <c r="AK153" t="n">
-        <v>3633</v>
+        <v>3661.2</v>
       </c>
       <c r="AL153" t="n">
-        <v>5.199999999999818</v>
+        <v>-23</v>
       </c>
       <c r="AM153" t="n">
-        <v>0.1429278214501626</v>
+        <v>-0.6321807487218954</v>
       </c>
       <c r="AN153" t="b">
         <v>0</v>
@@ -20827,32 +20827,32 @@
         </is>
       </c>
       <c r="AF154" t="n">
-        <v>2503.8</v>
+        <v>2546.5</v>
       </c>
       <c r="AG154" t="n">
-        <v>2481</v>
+        <v>2482.4</v>
       </c>
       <c r="AH154" t="n">
-        <v>2486.1</v>
+        <v>2519</v>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK154" t="n">
-        <v>2486.1</v>
+        <v>2535.516</v>
       </c>
       <c r="AL154" t="n">
-        <v>-0.2999999999997271</v>
+        <v>-49.71599999999989</v>
       </c>
       <c r="AM154" t="n">
-        <v>-0.0120685493603559</v>
+        <v>-1.999999999999996</v>
       </c>
       <c r="AN154" t="b">
         <v>0</v>
@@ -20959,32 +20959,32 @@
         </is>
       </c>
       <c r="AF155" t="n">
-        <v>1561.9</v>
+        <v>1598.7</v>
       </c>
       <c r="AG155" t="n">
-        <v>1544.1</v>
+        <v>1545</v>
       </c>
       <c r="AH155" t="n">
-        <v>1555.1</v>
+        <v>1582.9</v>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK155" t="n">
-        <v>1555.1</v>
+        <v>1587.732</v>
       </c>
       <c r="AL155" t="n">
-        <v>1.5</v>
+        <v>-31.13200000000007</v>
       </c>
       <c r="AM155" t="n">
-        <v>0.0963638699730181</v>
+        <v>-2.000000000000004</v>
       </c>
       <c r="AN155" t="b">
         <v>0</v>
@@ -21091,13 +21091,13 @@
         </is>
       </c>
       <c r="AF156" t="n">
-        <v>429.9</v>
+        <v>427.05</v>
       </c>
       <c r="AG156" t="n">
-        <v>426.8</v>
+        <v>422.7</v>
       </c>
       <c r="AH156" t="n">
-        <v>427.25</v>
+        <v>426.2</v>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
@@ -21110,13 +21110,13 @@
         </is>
       </c>
       <c r="AK156" t="n">
-        <v>427.25</v>
+        <v>426.2</v>
       </c>
       <c r="AL156" t="n">
-        <v>-0.1499999999999772</v>
+        <v>0.9000000000000341</v>
       </c>
       <c r="AM156" t="n">
-        <v>-0.0351205806602615</v>
+        <v>0.2107234839616095</v>
       </c>
       <c r="AN156" t="b">
         <v>0</v>
@@ -21223,13 +21223,13 @@
         </is>
       </c>
       <c r="AF157" t="n">
-        <v>253.48</v>
+        <v>254.2</v>
       </c>
       <c r="AG157" t="n">
-        <v>250.45</v>
+        <v>248.9</v>
       </c>
       <c r="AH157" t="n">
-        <v>250.75</v>
+        <v>249.5</v>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
@@ -21242,13 +21242,13 @@
         </is>
       </c>
       <c r="AK157" t="n">
-        <v>250.75</v>
+        <v>249.5</v>
       </c>
       <c r="AL157" t="n">
-        <v>0.0500000000000113</v>
+        <v>1.300000000000011</v>
       </c>
       <c r="AM157" t="n">
-        <v>0.0199362041467349</v>
+        <v>0.5183413078149965</v>
       </c>
       <c r="AN157" t="b">
         <v>0</v>
@@ -21351,13 +21351,13 @@
         </is>
       </c>
       <c r="AF158" t="n">
-        <v>851.45</v>
+        <v>856.55</v>
       </c>
       <c r="AG158" t="n">
-        <v>843.7</v>
+        <v>842.8</v>
       </c>
       <c r="AH158" t="n">
-        <v>851.45</v>
+        <v>853.8</v>
       </c>
       <c r="AI158" t="inlineStr">
         <is>
@@ -21370,13 +21370,13 @@
         </is>
       </c>
       <c r="AK158" t="n">
-        <v>851.45</v>
+        <v>853.8</v>
       </c>
       <c r="AL158" t="n">
-        <v>0.2999999999999545</v>
+        <v>-2.049999999999955</v>
       </c>
       <c r="AM158" t="n">
-        <v>0.0352216025829121</v>
+        <v>-0.2406809509832644</v>
       </c>
       <c r="AN158" t="b">
         <v>0</v>
@@ -21483,32 +21483,32 @@
         </is>
       </c>
       <c r="AF159" t="n">
-        <v>124.6</v>
+        <v>127.85</v>
       </c>
       <c r="AG159" t="n">
-        <v>123</v>
+        <v>123.85</v>
       </c>
       <c r="AH159" t="n">
-        <v>124.27</v>
+        <v>126.74</v>
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK159" t="n">
-        <v>124.27</v>
+        <v>126.6636</v>
       </c>
       <c r="AL159" t="n">
-        <v>-0.0899999999999892</v>
+        <v>-2.483599999999996</v>
       </c>
       <c r="AM159" t="n">
-        <v>-0.0724754388790378</v>
+        <v>-1.999999999999996</v>
       </c>
       <c r="AN159" t="b">
         <v>0</v>
@@ -21615,32 +21615,32 @@
         </is>
       </c>
       <c r="AF160" t="n">
-        <v>1223.8</v>
+        <v>1242.3</v>
       </c>
       <c r="AG160" t="n">
-        <v>1213.7</v>
+        <v>1218.7</v>
       </c>
       <c r="AH160" t="n">
-        <v>1216.9</v>
+        <v>1236</v>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK160" t="n">
-        <v>1216.9</v>
+        <v>1241.952</v>
       </c>
       <c r="AL160" t="n">
-        <v>0.6999999999998181</v>
+        <v>-24.35200000000009</v>
       </c>
       <c r="AM160" t="n">
-        <v>0.0574901445466342</v>
+        <v>-2.000000000000007</v>
       </c>
       <c r="AN160" t="b">
         <v>0</v>
@@ -21747,13 +21747,13 @@
         </is>
       </c>
       <c r="AF161" t="n">
-        <v>1876.2</v>
+        <v>1900.7</v>
       </c>
       <c r="AG161" t="n">
-        <v>1867.7</v>
+        <v>1871.2</v>
       </c>
       <c r="AH161" t="n">
-        <v>1871.2</v>
+        <v>1883.9</v>
       </c>
       <c r="AI161" t="inlineStr">
         <is>
@@ -21766,13 +21766,13 @@
         </is>
       </c>
       <c r="AK161" t="n">
-        <v>1871.2</v>
+        <v>1883.9</v>
       </c>
       <c r="AL161" t="n">
-        <v>-0.6000000000001364</v>
+        <v>-13.30000000000018</v>
       </c>
       <c r="AM161" t="n">
-        <v>-0.0320752699668628</v>
+        <v>-0.7110018175986412</v>
       </c>
       <c r="AN161" t="b">
         <v>0</v>
@@ -21879,35 +21879,35 @@
         </is>
       </c>
       <c r="AF162" t="n">
-        <v>1146.35</v>
+        <v>1117.15</v>
       </c>
       <c r="AG162" t="n">
-        <v>1130</v>
+        <v>1083.25</v>
       </c>
       <c r="AH162" t="n">
-        <v>1134.4</v>
+        <v>1097.5</v>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>TARGET HIT</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Target reached during replay range</t>
         </is>
       </c>
       <c r="AK162" t="n">
-        <v>1134.4</v>
+        <v>1089.264</v>
       </c>
       <c r="AL162" t="n">
-        <v>0.25</v>
+        <v>45.3860000000002</v>
       </c>
       <c r="AM162" t="n">
-        <v>0.0220332261049662</v>
+        <v>4.000000000000017</v>
       </c>
       <c r="AN162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -22011,32 +22011,32 @@
         </is>
       </c>
       <c r="AF163" t="n">
-        <v>1846</v>
+        <v>1903</v>
       </c>
       <c r="AG163" t="n">
-        <v>1836.8</v>
+        <v>1838.1</v>
       </c>
       <c r="AH163" t="n">
-        <v>1839.1</v>
+        <v>1867</v>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK163" t="n">
-        <v>1839.1</v>
+        <v>1871.904</v>
       </c>
       <c r="AL163" t="n">
-        <v>-3.899999999999864</v>
+        <v>-36.70399999999995</v>
       </c>
       <c r="AM163" t="n">
-        <v>-0.2125108979947615</v>
+        <v>-1.999999999999997</v>
       </c>
       <c r="AN163" t="b">
         <v>0</v>
@@ -22143,32 +22143,32 @@
         </is>
       </c>
       <c r="AF164" t="n">
-        <v>141.45</v>
+        <v>144.17</v>
       </c>
       <c r="AG164" t="n">
-        <v>140.56</v>
+        <v>140.5</v>
       </c>
       <c r="AH164" t="n">
-        <v>141.08</v>
+        <v>143.48</v>
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK164" t="n">
-        <v>141.08</v>
+        <v>143.7792</v>
       </c>
       <c r="AL164" t="n">
-        <v>-0.1200000000000045</v>
+        <v>-2.819199999999995</v>
       </c>
       <c r="AM164" t="n">
-        <v>-0.08513053348467969</v>
+        <v>-1.999999999999996</v>
       </c>
       <c r="AN164" t="b">
         <v>0</v>
@@ -22275,13 +22275,13 @@
         </is>
       </c>
       <c r="AF165" t="n">
-        <v>1023.7</v>
+        <v>1023.5</v>
       </c>
       <c r="AG165" t="n">
-        <v>1001.7</v>
+        <v>1000.7</v>
       </c>
       <c r="AH165" t="n">
-        <v>1015.4</v>
+        <v>1018.9</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
@@ -22294,13 +22294,13 @@
         </is>
       </c>
       <c r="AK165" t="n">
-        <v>1015.4</v>
+        <v>1018.9</v>
       </c>
       <c r="AL165" t="n">
-        <v>1.300000000000068</v>
+        <v>-2.199999999999932</v>
       </c>
       <c r="AM165" t="n">
-        <v>0.1278646601750829</v>
+        <v>-0.2163863479885838</v>
       </c>
       <c r="AN165" t="b">
         <v>0</v>
@@ -22407,32 +22407,32 @@
         </is>
       </c>
       <c r="AF166" t="n">
-        <v>725.45</v>
+        <v>732</v>
       </c>
       <c r="AG166" t="n">
-        <v>715.2</v>
+        <v>717.15</v>
       </c>
       <c r="AH166" t="n">
-        <v>717.5</v>
+        <v>730.45</v>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK166" t="n">
-        <v>717.5</v>
+        <v>731.2890000000001</v>
       </c>
       <c r="AL166" t="n">
-        <v>-0.5499999999999545</v>
+        <v>-14.33900000000006</v>
       </c>
       <c r="AM166" t="n">
-        <v>-0.076713857312219</v>
+        <v>-2.000000000000008</v>
       </c>
       <c r="AN166" t="b">
         <v>0</v>
@@ -22539,13 +22539,13 @@
         </is>
       </c>
       <c r="AF167" t="n">
-        <v>344.3</v>
+        <v>347.25</v>
       </c>
       <c r="AG167" t="n">
-        <v>341.5</v>
+        <v>341.4</v>
       </c>
       <c r="AH167" t="n">
-        <v>343.25</v>
+        <v>346.2</v>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
@@ -22558,13 +22558,13 @@
         </is>
       </c>
       <c r="AK167" t="n">
-        <v>343.25</v>
+        <v>346.2</v>
       </c>
       <c r="AL167" t="n">
-        <v>-0.3000000000000113</v>
+        <v>-3.25</v>
       </c>
       <c r="AM167" t="n">
-        <v>-0.08747630849978461</v>
+        <v>-0.9476600087476308</v>
       </c>
       <c r="AN167" t="b">
         <v>0</v>
@@ -22671,13 +22671,13 @@
         </is>
       </c>
       <c r="AF168" t="n">
-        <v>354</v>
+        <v>355.75</v>
       </c>
       <c r="AG168" t="n">
-        <v>351</v>
+        <v>350.65</v>
       </c>
       <c r="AH168" t="n">
-        <v>351.85</v>
+        <v>355.3</v>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
@@ -22690,13 +22690,13 @@
         </is>
       </c>
       <c r="AK168" t="n">
-        <v>351.85</v>
+        <v>355.3</v>
       </c>
       <c r="AL168" t="n">
-        <v>-0.0500000000000113</v>
+        <v>-3.5</v>
       </c>
       <c r="AM168" t="n">
-        <v>-0.01421262080728</v>
+        <v>-0.9948834565093804</v>
       </c>
       <c r="AN168" t="b">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="AF169" t="n">
-        <v>537.95</v>
+        <v>533.5</v>
       </c>
       <c r="AG169" t="n">
-        <v>530</v>
+        <v>521.5</v>
       </c>
       <c r="AH169" t="n">
-        <v>532</v>
+        <v>529.55</v>
       </c>
       <c r="AI169" t="inlineStr">
         <is>
@@ -22822,13 +22822,13 @@
         </is>
       </c>
       <c r="AK169" t="n">
-        <v>532</v>
+        <v>529.55</v>
       </c>
       <c r="AL169" t="n">
-        <v>-0.5499999999999545</v>
+        <v>1.900000000000091</v>
       </c>
       <c r="AM169" t="n">
-        <v>-0.1034904506538629</v>
+        <v>0.3575124658952095</v>
       </c>
       <c r="AN169" t="b">
         <v>0</v>
@@ -22935,32 +22935,32 @@
         </is>
       </c>
       <c r="AF170" t="n">
-        <v>1001.6</v>
+        <v>1007.35</v>
       </c>
       <c r="AG170" t="n">
-        <v>986.85</v>
+        <v>987.6</v>
       </c>
       <c r="AH170" t="n">
-        <v>987.65</v>
+        <v>1001.85</v>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK170" t="n">
-        <v>987.65</v>
+        <v>1005.72</v>
       </c>
       <c r="AL170" t="n">
-        <v>-1.649999999999977</v>
+        <v>-19.72000000000003</v>
       </c>
       <c r="AM170" t="n">
-        <v>-0.1673427991886386</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AN170" t="b">
         <v>0</v>
@@ -23067,13 +23067,13 @@
         </is>
       </c>
       <c r="AF171" t="n">
-        <v>945.4</v>
+        <v>955</v>
       </c>
       <c r="AG171" t="n">
-        <v>940.4</v>
+        <v>931.65</v>
       </c>
       <c r="AH171" t="n">
-        <v>941.95</v>
+        <v>951.7</v>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
@@ -23086,13 +23086,13 @@
         </is>
       </c>
       <c r="AK171" t="n">
-        <v>941.95</v>
+        <v>951.7</v>
       </c>
       <c r="AL171" t="n">
-        <v>-1.25</v>
+        <v>-11</v>
       </c>
       <c r="AM171" t="n">
-        <v>-0.1328797703837567</v>
+        <v>-1.16934197937706</v>
       </c>
       <c r="AN171" t="b">
         <v>0</v>
@@ -23199,13 +23199,13 @@
         </is>
       </c>
       <c r="AF172" t="n">
-        <v>10940</v>
+        <v>10890</v>
       </c>
       <c r="AG172" t="n">
-        <v>10693</v>
+        <v>10568</v>
       </c>
       <c r="AH172" t="n">
-        <v>10793</v>
+        <v>10682</v>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
@@ -23218,13 +23218,13 @@
         </is>
       </c>
       <c r="AK172" t="n">
-        <v>10793</v>
+        <v>10682</v>
       </c>
       <c r="AL172" t="n">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="AM172" t="n">
-        <v>0.1480247941530206</v>
+        <v>1.174946803589601</v>
       </c>
       <c r="AN172" t="b">
         <v>0</v>
@@ -23327,13 +23327,13 @@
         </is>
       </c>
       <c r="AF173" t="n">
-        <v>79.48</v>
+        <v>78.38</v>
       </c>
       <c r="AG173" t="n">
-        <v>78.84</v>
+        <v>77.14</v>
       </c>
       <c r="AH173" t="n">
-        <v>78.87</v>
+        <v>78.06</v>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
@@ -23346,13 +23346,13 @@
         </is>
       </c>
       <c r="AK173" t="n">
-        <v>78.87</v>
+        <v>78.06</v>
       </c>
       <c r="AL173" t="n">
-        <v>0.1199999999999903</v>
+        <v>0.9299999999999926</v>
       </c>
       <c r="AM173" t="n">
-        <v>0.1519179642992661</v>
+        <v>1.177364223319398</v>
       </c>
       <c r="AN173" t="b">
         <v>0</v>
@@ -23459,32 +23459,32 @@
         </is>
       </c>
       <c r="AF174" t="n">
-        <v>389.25</v>
+        <v>397.5</v>
       </c>
       <c r="AG174" t="n">
-        <v>386</v>
+        <v>387.4</v>
       </c>
       <c r="AH174" t="n">
-        <v>388.3</v>
+        <v>396</v>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK174" t="n">
-        <v>388.3</v>
+        <v>395.454</v>
       </c>
       <c r="AL174" t="n">
-        <v>-0.6000000000000227</v>
+        <v>-7.754000000000019</v>
       </c>
       <c r="AM174" t="n">
-        <v>-0.1547588341501219</v>
+        <v>-2.000000000000005</v>
       </c>
       <c r="AN174" t="b">
         <v>0</v>
@@ -23591,13 +23591,13 @@
         </is>
       </c>
       <c r="AF175" t="n">
-        <v>3104.8</v>
+        <v>3107.4</v>
       </c>
       <c r="AG175" t="n">
-        <v>3081.6</v>
+        <v>3076.3</v>
       </c>
       <c r="AH175" t="n">
-        <v>3090</v>
+        <v>3094.4</v>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
@@ -23610,13 +23610,13 @@
         </is>
       </c>
       <c r="AK175" t="n">
-        <v>3090</v>
+        <v>3094.4</v>
       </c>
       <c r="AL175" t="n">
-        <v>-1.5</v>
+        <v>-5.900000000000091</v>
       </c>
       <c r="AM175" t="n">
-        <v>-0.0485672656629431</v>
+        <v>-0.1910312449409127</v>
       </c>
       <c r="AN175" t="b">
         <v>0</v>
@@ -23719,32 +23719,32 @@
         </is>
       </c>
       <c r="AF176" t="n">
-        <v>161.34</v>
+        <v>163.98</v>
       </c>
       <c r="AG176" t="n">
-        <v>159.27</v>
+        <v>158.53</v>
       </c>
       <c r="AH176" t="n">
-        <v>159.91</v>
+        <v>162.53</v>
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK176" t="n">
-        <v>159.91</v>
+        <v>163.047</v>
       </c>
       <c r="AL176" t="n">
-        <v>-0.0600000000000022</v>
+        <v>-3.197000000000003</v>
       </c>
       <c r="AM176" t="n">
-        <v>-0.0375351892399138</v>
+        <v>-2.000000000000002</v>
       </c>
       <c r="AN176" t="b">
         <v>0</v>
@@ -23851,13 +23851,13 @@
         </is>
       </c>
       <c r="AF177" t="n">
-        <v>949.8</v>
+        <v>954.85</v>
       </c>
       <c r="AG177" t="n">
-        <v>943.65</v>
+        <v>945.75</v>
       </c>
       <c r="AH177" t="n">
-        <v>945.9</v>
+        <v>949.3</v>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
@@ -23870,13 +23870,13 @@
         </is>
       </c>
       <c r="AK177" t="n">
-        <v>945.9</v>
+        <v>949.3</v>
       </c>
       <c r="AL177" t="n">
-        <v>0.3999999999999772</v>
+        <v>-3</v>
       </c>
       <c r="AM177" t="n">
-        <v>0.042269893268517</v>
+        <v>-0.3170241995138962</v>
       </c>
       <c r="AN177" t="b">
         <v>0</v>
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="AF178" t="n">
-        <v>8875</v>
+        <v>8910</v>
       </c>
       <c r="AG178" t="n">
-        <v>8790.5</v>
+        <v>8837.5</v>
       </c>
       <c r="AH178" t="n">
-        <v>8860</v>
+        <v>8855</v>
       </c>
       <c r="AI178" t="inlineStr">
         <is>
@@ -24002,13 +24002,13 @@
         </is>
       </c>
       <c r="AK178" t="n">
-        <v>8860</v>
+        <v>8855</v>
       </c>
       <c r="AL178" t="n">
-        <v>-4.5</v>
+        <v>0.5</v>
       </c>
       <c r="AM178" t="n">
-        <v>-0.0508158771385015</v>
+        <v>0.0056462085709446</v>
       </c>
       <c r="AN178" t="b">
         <v>0</v>
@@ -24111,32 +24111,32 @@
         </is>
       </c>
       <c r="AF179" t="n">
-        <v>82.81999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="AG179" t="n">
-        <v>82</v>
+        <v>82.19</v>
       </c>
       <c r="AH179" t="n">
-        <v>82.52</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK179" t="n">
-        <v>82.52</v>
+        <v>84.099</v>
       </c>
       <c r="AL179" t="n">
-        <v>-0.0699999999999931</v>
+        <v>-1.649000000000001</v>
       </c>
       <c r="AM179" t="n">
-        <v>-0.08489993935717779</v>
+        <v>-2.000000000000001</v>
       </c>
       <c r="AN179" t="b">
         <v>0</v>
@@ -24243,32 +24243,32 @@
         </is>
       </c>
       <c r="AF180" t="n">
-        <v>633.05</v>
+        <v>643.9</v>
       </c>
       <c r="AG180" t="n">
         <v>626.15</v>
       </c>
       <c r="AH180" t="n">
-        <v>627.2</v>
+        <v>641.25</v>
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>EOD EXIT</t>
+          <t>STOP LOSS HIT</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>Neither target nor stop reached; exited at close</t>
+          <t>Stop loss breached during replay range</t>
         </is>
       </c>
       <c r="AK180" t="n">
-        <v>627.2</v>
+        <v>637.5</v>
       </c>
       <c r="AL180" t="n">
-        <v>-2.200000000000045</v>
+        <v>-12.5</v>
       </c>
       <c r="AM180" t="n">
-        <v>-0.3520000000000072</v>
+        <v>-2</v>
       </c>
       <c r="AN180" t="b">
         <v>0</v>
@@ -24375,13 +24375,13 @@
         </is>
       </c>
       <c r="AF181" t="n">
-        <v>1242.8</v>
+        <v>1251.8</v>
       </c>
       <c r="AG181" t="n">
-        <v>1231.4</v>
+        <v>1234.1</v>
       </c>
       <c r="AH181" t="n">
-        <v>1239.3</v>
+        <v>1248.9</v>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
@@ -24394,13 +24394,13 @@
         </is>
       </c>
       <c r="AK181" t="n">
-        <v>1239.3</v>
+        <v>1248.9</v>
       </c>
       <c r="AL181" t="n">
-        <v>-0.7999999999999545</v>
+        <v>-10.40000000000009</v>
       </c>
       <c r="AM181" t="n">
-        <v>-0.06459426725877709</v>
+        <v>-0.8397254743641576</v>
       </c>
       <c r="AN181" t="b">
         <v>0</v>
@@ -24507,13 +24507,13 @@
         </is>
       </c>
       <c r="AF182" t="n">
-        <v>1104.3</v>
+        <v>1114.2</v>
       </c>
       <c r="AG182" t="n">
-        <v>1090</v>
+        <v>1074.1</v>
       </c>
       <c r="AH182" t="n">
-        <v>1100.3</v>
+        <v>1106.7</v>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
@@ -24526,13 +24526,13 @@
         </is>
       </c>
       <c r="AK182" t="n">
-        <v>1100.3</v>
+        <v>1106.7</v>
       </c>
       <c r="AL182" t="n">
-        <v>1.100000000000136</v>
+        <v>-5.299999999999955</v>
       </c>
       <c r="AM182" t="n">
-        <v>0.099872889050312</v>
+        <v>-0.4812057381514394</v>
       </c>
       <c r="AN182" t="b">
         <v>0</v>
@@ -24587,7 +24587,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-2</v>
+        <v>-1.447708989157049</v>
       </c>
     </row>
     <row r="3">
@@ -24600,10 +24600,10 @@
         <v>76</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.108159851839941</v>
+        <v>-0.4793545292967923</v>
       </c>
     </row>
     <row r="4">
@@ -24619,7 +24619,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1645100302011018</v>
+        <v>1.529697743511669</v>
       </c>
     </row>
     <row r="5">
@@ -24632,10 +24632,10 @@
         <v>102</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1548776664646863</v>
+        <v>-0.8744991631709124</v>
       </c>
     </row>
   </sheetData>
